--- a/lambda_perturbation_result.xlsx
+++ b/lambda_perturbation_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitra\Downloads\matlab analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D79D3A-6B15-48D9-983B-01FF1ADCFABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA1A5CB-C6AD-42E7-A221-3DA031B22DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="50" activeTab="50" xr2:uid="{54EEB03B-E474-4362-ABD5-5443D823EEF5}"/>
   </bookViews>
@@ -7085,28 +7085,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>280.33999999999997</v>
+        <v>242.2</v>
       </c>
       <c r="B2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="C2">
-        <v>67.083028629233141</v>
+        <v>113.753388492073</v>
       </c>
       <c r="D2">
-        <v>-1.5475239982848096E-2</v>
+        <v>-18.633758627701685</v>
       </c>
       <c r="E2">
-        <v>0.26845305433424982</v>
+        <v>41.741352574135156</v>
       </c>
       <c r="F2">
-        <v>0.26845305433424982</v>
+        <v>41.741352574135156</v>
       </c>
       <c r="G2">
-        <v>0.11934897733253454</v>
+        <v>58.024449111202259</v>
       </c>
       <c r="H2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I2">
         <v>3</v>
@@ -7405,16 +7405,16 @@
         <v>0.3</v>
       </c>
       <c r="B2">
-        <v>3.0000000000000001E-5</v>
+        <v>0.03</v>
       </c>
       <c r="C2">
-        <v>73.55633819321686</v>
+        <v>92.55685664962833</v>
       </c>
       <c r="D2">
-        <v>1518.2620771458937</v>
+        <v>1527.6155209372105</v>
       </c>
       <c r="E2">
-        <v>6.0146678046458089E-2</v>
+        <v>-18.633758627701685</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7422,16 +7422,16 @@
         <v>0.5</v>
       </c>
       <c r="B3">
-        <v>5.0000000000000002E-5</v>
+        <v>0.05</v>
       </c>
       <c r="C3">
-        <v>73.529655426763583</v>
+        <v>100.20681716938664</v>
       </c>
       <c r="D3">
-        <v>1518.4028727611751</v>
+        <v>1529.8374653683991</v>
       </c>
       <c r="E3">
-        <v>2.3849581281285562E-2</v>
+        <v>-11.908718942144185</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -7439,16 +7439,16 @@
         <v>0.7</v>
       </c>
       <c r="B4">
-        <v>6.9999999999999994E-5</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="C4">
-        <v>73.527238181884897</v>
+        <v>106.16424617256973</v>
       </c>
       <c r="D4">
-        <v>1518.4700560765048</v>
+        <v>1531.462377004673</v>
       </c>
       <c r="E4">
-        <v>2.0561355099026412E-2</v>
+        <v>-6.6715747285472045</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -7456,13 +7456,13 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="C5">
-        <v>73.512123093214868</v>
+        <v>113.753388492073</v>
       </c>
       <c r="D5">
-        <v>1518.5961063205477</v>
+        <v>1533.3410463484852</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -7473,16 +7473,16 @@
         <v>1.5</v>
       </c>
       <c r="B6">
-        <v>1.5000000000000001E-4</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="C6">
-        <v>73.503156809171657</v>
+        <v>125.3699453669919</v>
       </c>
       <c r="D6">
-        <v>1518.7345029817425</v>
+        <v>1535.7688831277887</v>
       </c>
       <c r="E6">
-        <v>-1.2197014133086284E-2</v>
+        <v>10.212053485974538</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -7490,16 +7490,16 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>2.0000000000000001E-4</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>73.501600769729805</v>
+        <v>137.33396037359543</v>
       </c>
       <c r="D7">
-        <v>1518.8236282199273</v>
+        <v>1537.5984987668135</v>
       </c>
       <c r="E7">
-        <v>-1.4313725467730182E-2</v>
+        <v>20.729555571142978</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -7507,16 +7507,16 @@
         <v>3</v>
       </c>
       <c r="B8">
-        <v>3.0000000000000003E-4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="C8">
-        <v>73.474392965155062</v>
+        <v>161.23559144757488</v>
       </c>
       <c r="D8">
-        <v>1519.0400744934484</v>
+        <v>1540.3585303842765</v>
       </c>
       <c r="E8">
-        <v>-5.1325042009688064E-2</v>
+        <v>41.741352574135156</v>
       </c>
     </row>
   </sheetData>

--- a/lambda_perturbation_result.xlsx
+++ b/lambda_perturbation_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitra\Downloads\matlab analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA1A5CB-C6AD-42E7-A221-3DA031B22DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F95E91-1963-4AD6-8B9B-090A38572D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="50" activeTab="50" xr2:uid="{54EEB03B-E474-4362-ABD5-5443D823EEF5}"/>
   </bookViews>
@@ -68,6 +68,23 @@
     <sheet name="LAMBDA_219p7K" sheetId="53" r:id="rId53"/>
     <sheet name="LAMBDA_249p6K" sheetId="54" r:id="rId54"/>
     <sheet name="LAMBDA_280p3K" sheetId="55" r:id="rId55"/>
+    <sheet name="LAMBDA_190p4K" sheetId="56" r:id="rId56"/>
+    <sheet name="LAMBDA_199p6K" sheetId="57" r:id="rId57"/>
+    <sheet name="LAMBDA_200p4K" sheetId="58" r:id="rId58"/>
+    <sheet name="LAMBDA_209p6K" sheetId="59" r:id="rId59"/>
+    <sheet name="LAMBDA_210p1K" sheetId="60" r:id="rId60"/>
+    <sheet name="LAMBDA_229p5K" sheetId="61" r:id="rId61"/>
+    <sheet name="LAMBDA_230p2K" sheetId="62" r:id="rId62"/>
+    <sheet name="LAMBDA_236p5K" sheetId="63" r:id="rId63"/>
+    <sheet name="LAMBDA_239p9K" sheetId="64" r:id="rId64"/>
+    <sheet name="LAMBDA_250p3K" sheetId="65" r:id="rId65"/>
+    <sheet name="LAMBDA_259p5K" sheetId="66" r:id="rId66"/>
+    <sheet name="LAMBDA_260p3K" sheetId="67" r:id="rId67"/>
+    <sheet name="LAMBDA_269p6K" sheetId="68" r:id="rId68"/>
+    <sheet name="LAMBDA_270p3K" sheetId="69" r:id="rId69"/>
+    <sheet name="LAMBDA_279p6K" sheetId="70" r:id="rId70"/>
+    <sheet name="LAMBDA_284p4K" sheetId="71" r:id="rId71"/>
+    <sheet name="LAMBDA_280p5K" sheetId="72" r:id="rId72"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="14">
   <si>
     <t>factor_vs_ref</t>
   </si>
@@ -515,7 +532,7 @@
         <v>1417.0274602694653</v>
       </c>
       <c r="E2">
-        <v>-0.52195765391470272</v>
+        <v>-99.362112237434928</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -532,7 +549,7 @@
         <v>1417.0341950822967</v>
       </c>
       <c r="E3">
-        <v>-0.33567574489063046</v>
+        <v>-99.360917733126726</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -549,7 +566,7 @@
         <v>1417.0386458910978</v>
       </c>
       <c r="E4">
-        <v>-0.18743228488966004</v>
+        <v>-99.359967144566824</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -566,7 +583,7 @@
         <v>1417.0470182514148</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.358765263648976</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -583,7 +600,7 @@
         <v>1417.0701212082597</v>
       </c>
       <c r="E6">
-        <v>0.26239282314930651</v>
+        <v>-99.35708270972124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -600,7 +617,7 @@
         <v>1417.0965517904526</v>
       </c>
       <c r="E7">
-        <v>0.48930198975888556</v>
+        <v>-99.355627689324976</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -617,7 +634,7 @@
         <v>1417.1436540011105</v>
       </c>
       <c r="E8">
-        <v>0.92652379576762245</v>
+        <v>-99.352824071229961</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +678,7 @@
         <v>1415.1190661000644</v>
       </c>
       <c r="E2">
-        <v>-0.35780241735567758</v>
+        <v>-99.335223322480687</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -678,7 +695,7 @@
         <v>1415.1220579967653</v>
       </c>
       <c r="E3">
-        <v>-0.22978605049738676</v>
+        <v>-99.334369243615583</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -695,7 +712,7 @@
         <v>1415.132757330884</v>
       </c>
       <c r="E4">
-        <v>-0.13357079478141412</v>
+        <v>-99.333727330253836</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -712,7 +729,7 @@
         <v>1415.1479489400842</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.332836194256018</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -729,7 +746,7 @@
         <v>1415.1732815971097</v>
       </c>
       <c r="E6">
-        <v>0.21310176563821565</v>
+        <v>-99.331414456406279</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -746,7 +763,7 @@
         <v>1415.1973403847596</v>
       </c>
       <c r="E7">
-        <v>0.41475348144981311</v>
+        <v>-99.330069109144716</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -763,7 +780,7 @@
         <v>1415.2476132170798</v>
       </c>
       <c r="E8">
-        <v>0.80602353317828968</v>
+        <v>-99.327458696976862</v>
       </c>
     </row>
   </sheetData>
@@ -807,7 +824,7 @@
         <v>1413.6810926700125</v>
       </c>
       <c r="E2">
-        <v>-0.4254740599668918</v>
+        <v>-99.332126038868466</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -824,7 +841,7 @@
         <v>1413.6861659702122</v>
       </c>
       <c r="E3">
-        <v>-0.26619491617351038</v>
+        <v>-99.331057709477122</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -841,7 +858,7 @@
         <v>1413.6937385257158</v>
       </c>
       <c r="E4">
-        <v>-0.15094334671874016</v>
+        <v>-99.330284685237302</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -858,7 +875,7 @@
         <v>1413.7067895333396</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.329272266348781</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -875,7 +892,7 @@
         <v>1413.730548170565</v>
       </c>
       <c r="E6">
-        <v>0.19219045027355044</v>
+        <v>-99.327983191697371</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -892,7 +909,7 @@
         <v>1413.7542437537795</v>
       </c>
       <c r="E7">
-        <v>0.38094040667987866</v>
+        <v>-99.326717193392483</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -909,7 +926,7 @@
         <v>1413.8076848265673</v>
       </c>
       <c r="E8">
-        <v>0.77662464410786658</v>
+        <v>-99.324063229474376</v>
       </c>
     </row>
   </sheetData>
@@ -953,7 +970,7 @@
         <v>1434.8245073526871</v>
       </c>
       <c r="E2">
-        <v>-0.28275767791152873</v>
+        <v>-99.283916762275609</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -970,7 +987,7 @@
         <v>1434.8327365867835</v>
       </c>
       <c r="E3">
-        <v>-0.19833651548181333</v>
+        <v>-99.28331052229224</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -987,7 +1004,7 @@
         <v>1434.8397040880311</v>
       </c>
       <c r="E4">
-        <v>-0.11840355453250201</v>
+        <v>-99.282736512701277</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1004,7 +1021,7 @@
         <v>1434.8496565492828</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.281886240484425</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1021,7 +1038,7 @@
         <v>1434.865862421387</v>
       </c>
       <c r="E6">
-        <v>0.19662872904597176</v>
+        <v>-99.280474222525982</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1038,7 +1055,7 @@
         <v>1434.8863447216102</v>
       </c>
       <c r="E7">
-        <v>0.38749843440768789</v>
+        <v>-99.27910356090905</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1055,7 +1072,7 @@
         <v>1434.9202762714235</v>
       </c>
       <c r="E8">
-        <v>0.81308901720508875</v>
+        <v>-99.276047336374774</v>
       </c>
     </row>
   </sheetData>
@@ -1099,7 +1116,7 @@
         <v>1432.7967461690453</v>
       </c>
       <c r="E2">
-        <v>-0.54420697764468362</v>
+        <v>-99.29157309387999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1116,7 +1133,7 @@
         <v>1432.7992869535046</v>
       </c>
       <c r="E3">
-        <v>-0.37021844291402728</v>
+        <v>-99.290333767787331</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1133,7 +1150,7 @@
         <v>1432.8023427650169</v>
       </c>
       <c r="E4">
-        <v>-0.21820092750826409</v>
+        <v>-99.289250941992648</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1150,7 +1167,7 @@
         <v>1432.8085918499703</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.287696689562594</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1167,7 +1184,7 @@
         <v>1432.821401968991</v>
       </c>
       <c r="E6">
-        <v>0.31955201941191047</v>
+        <v>-99.285420509949759</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1184,7 +1201,7 @@
         <v>1432.8376042550331</v>
       </c>
       <c r="E7">
-        <v>0.58649721332823745</v>
+        <v>-99.283519050496437</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1201,7 +1218,7 @@
         <v>1432.8662078059519</v>
       </c>
       <c r="E8">
-        <v>1.072170447364309</v>
+        <v>-99.280059583972474</v>
       </c>
     </row>
   </sheetData>
@@ -1245,7 +1262,7 @@
         <v>1429.6197168646991</v>
       </c>
       <c r="E2">
-        <v>-0.43518003252888821</v>
+        <v>-99.237504348887654</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1262,7 +1279,7 @@
         <v>1429.6261087195419</v>
       </c>
       <c r="E3">
-        <v>-0.28906503549891899</v>
+        <v>-99.236385358768118</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1279,7 +1296,7 @@
         <v>1429.6301308846898</v>
       </c>
       <c r="E4">
-        <v>-0.16609993142369689</v>
+        <v>-99.235443657099538</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1296,7 +1313,7 @@
         <v>1429.6357110811093</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.234171616680015</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1313,7 +1330,7 @@
         <v>1429.6476512660906</v>
       </c>
       <c r="E6">
-        <v>0.26793899939229104</v>
+        <v>-99.232119663772679</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1330,7 +1347,7 @@
         <v>1429.6607034355627</v>
       </c>
       <c r="E7">
-        <v>0.53426431999094293</v>
+        <v>-99.23008006887558</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1347,7 +1364,7 @@
         <v>1429.6826811235785</v>
       </c>
       <c r="E8">
-        <v>1.0211193464753201</v>
+        <v>-99.226351594897139</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1408,7 @@
         <v>1426.4109266094149</v>
       </c>
       <c r="E2">
-        <v>-0.62251766843598477</v>
+        <v>-99.249525538593801</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1408,7 +1425,7 @@
         <v>1426.4161298102711</v>
       </c>
       <c r="E3">
-        <v>-0.40242073858402716</v>
+        <v>-99.247863420365292</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1425,7 +1442,7 @@
         <v>1426.4197140563549</v>
       </c>
       <c r="E4">
-        <v>-0.21994898752980055</v>
+        <v>-99.246485438292467</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1442,7 +1459,7 @@
         <v>1426.4277383492456</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.244824437288216</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1459,7 +1476,7 @@
         <v>1426.4446297744414</v>
       </c>
       <c r="E6">
-        <v>0.31240417939496318</v>
+        <v>-99.242465237268547</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1476,7 +1493,7 @@
         <v>1426.4593913696056</v>
       </c>
       <c r="E7">
-        <v>0.59907949904878655</v>
+        <v>-99.240300335310181</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1493,7 +1510,7 @@
         <v>1426.484026360507</v>
       </c>
       <c r="E8">
-        <v>1.1080835240547577</v>
+        <v>-99.236456461300108</v>
       </c>
     </row>
   </sheetData>
@@ -1537,7 +1554,7 @@
         <v>1428.5658016162524</v>
       </c>
       <c r="E2">
-        <v>-6.0630882153010185E-2</v>
+        <v>-99.217286928920458</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1554,7 +1571,7 @@
         <v>1428.5758527699261</v>
       </c>
       <c r="E3">
-        <v>-6.1097931647602653E-2</v>
+        <v>-99.217290586795713</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1571,7 +1588,7 @@
         <v>1428.5865524796959</v>
       </c>
       <c r="E4">
-        <v>-4.891433038587871E-2</v>
+        <v>-99.217195166301806</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1588,7 +1605,7 @@
         <v>1428.6002874217754</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.216812075172726</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1605,7 +1622,7 @@
         <v>1428.6193215890009</v>
       </c>
       <c r="E6">
-        <v>0.15255356337800743</v>
+        <v>-99.215617294085462</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1622,7 +1639,7 @@
         <v>1428.6377221254834</v>
       </c>
       <c r="E7">
-        <v>0.3361926362874868</v>
+        <v>-99.214179055041171</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1639,7 +1656,7 @@
         <v>1428.6703742493085</v>
       </c>
       <c r="E8">
-        <v>0.7630223853144964</v>
+        <v>-99.210836175987225</v>
       </c>
     </row>
   </sheetData>
@@ -1683,7 +1700,7 @@
         <v>1431.7436965090042</v>
       </c>
       <c r="E2">
-        <v>-0.58803869091894012</v>
+        <v>-99.188718345567679</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1700,7 +1717,7 @@
         <v>1431.7542584916191</v>
       </c>
       <c r="E3">
-        <v>-0.37218796590093045</v>
+        <v>-99.186956829840625</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1717,7 +1734,7 @@
         <v>1431.766479668546</v>
       </c>
       <c r="E4">
-        <v>-0.20968324675262889</v>
+        <v>-99.185630660477628</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1734,7 +1751,7 @@
         <v>1431.7810422419177</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.183919476339497</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1751,7 +1768,7 @@
         <v>1431.7999689390738</v>
       </c>
       <c r="E6">
-        <v>0.32557355182986075</v>
+        <v>-99.181262533992822</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1768,7 +1785,7 @@
         <v>1431.8210417606845</v>
       </c>
       <c r="E7">
-        <v>0.57364731693525273</v>
+        <v>-99.17923805231149</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1785,7 +1802,7 @@
         <v>1431.85366359156</v>
       </c>
       <c r="E8">
-        <v>1.0733124320621066</v>
+        <v>-99.175160382623417</v>
       </c>
     </row>
   </sheetData>
@@ -1829,7 +1846,7 @@
         <v>1432.9955201333617</v>
       </c>
       <c r="E2">
-        <v>-0.55946611993065964</v>
+        <v>-99.139082429856529</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1846,7 +1863,7 @@
         <v>1433.0078720033212</v>
       </c>
       <c r="E3">
-        <v>-0.33989225876922019</v>
+        <v>-99.137181444537532</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1863,7 +1880,7 @@
         <v>1433.0186342152465</v>
       </c>
       <c r="E4">
-        <v>-0.17730312461748607</v>
+        <v>-99.135773810881091</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1880,7 +1897,7 @@
         <v>1433.0374095988009</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.134238789202612</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1897,7 +1914,7 @@
         <v>1433.0602375442083</v>
       </c>
       <c r="E6">
-        <v>0.28218971554503103</v>
+        <v>-99.131795700104547</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1914,7 +1931,7 @@
         <v>1433.07723918543</v>
       </c>
       <c r="E7">
-        <v>0.49006666468262783</v>
+        <v>-99.129995982112732</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1931,7 +1948,7 @@
         <v>1433.1142300525144</v>
       </c>
       <c r="E8">
-        <v>0.86242339106202792</v>
+        <v>-99.126772262009951</v>
       </c>
     </row>
   </sheetData>
@@ -1975,7 +1992,7 @@
         <v>1949.8517613828089</v>
       </c>
       <c r="E2">
-        <v>-4.990443334898198E-2</v>
+        <v>-98.880277999022042</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1992,7 +2009,7 @@
         <v>1949.8982293886449</v>
       </c>
       <c r="E3">
-        <v>-3.4946487491441136E-2</v>
+        <v>-98.880110427986011</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2009,7 +2026,7 @@
         <v>1949.5870125013166</v>
       </c>
       <c r="E4">
-        <v>-2.0091040580052379E-2</v>
+        <v>-98.87994400522625</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2026,7 +2043,7 @@
         <v>1949.6463116165303</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.879718929101699</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2043,7 +2060,7 @@
         <v>1950.482929264753</v>
       </c>
       <c r="E6">
-        <v>3.2007218975654832E-2</v>
+        <v>-98.879360358286192</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2060,7 +2077,7 @@
         <v>1950.772165948247</v>
       </c>
       <c r="E7">
-        <v>5.9232521551438572E-2</v>
+        <v>-98.879055358374941</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2077,7 +2094,7 @@
         <v>1950.6179010526384</v>
       </c>
       <c r="E8">
-        <v>0.10199004867855213</v>
+        <v>-98.878576353892157</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2138,7 @@
         <v>1434.3955403019772</v>
       </c>
       <c r="E2">
-        <v>-0.49398987613144923</v>
+        <v>-99.088649927712353</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2138,7 +2155,7 @@
         <v>1434.4168518887009</v>
       </c>
       <c r="E3">
-        <v>-0.31393361257147734</v>
+        <v>-99.087000838490425</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2155,7 +2172,7 @@
         <v>1434.4302832924977</v>
       </c>
       <c r="E4">
-        <v>-0.16746181482944256</v>
+        <v>-99.085659340793015</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2172,7 +2189,7 @@
         <v>1434.4469517811378</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.084125600902723</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2189,7 +2206,7 @@
         <v>1434.4791086613795</v>
       </c>
       <c r="E6">
-        <v>0.24176756233564822</v>
+        <v>-99.081911313693979</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2206,7 +2223,7 @@
         <v>1434.5029191926358</v>
       </c>
       <c r="E7">
-        <v>0.47664129606408567</v>
+        <v>-99.079760165296562</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2223,7 +2240,7 @@
         <v>1434.5409677726423</v>
       </c>
       <c r="E8">
-        <v>0.93634633443552151</v>
+        <v>-99.075549844538742</v>
       </c>
     </row>
   </sheetData>
@@ -2267,7 +2284,7 @@
         <v>1432.1355832810216</v>
       </c>
       <c r="E2">
-        <v>-0.29526209740143283</v>
+        <v>-99.084657420933425</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2284,7 +2301,7 @@
         <v>1432.1653315264648</v>
       </c>
       <c r="E3">
-        <v>-0.19608820454908121</v>
+        <v>-99.083746951794552</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2301,7 +2318,7 @@
         <v>1432.1866933427345</v>
       </c>
       <c r="E4">
-        <v>-0.11063638789057605</v>
+        <v>-99.082962458621097</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2318,7 +2335,7 @@
         <v>1432.2085626316352</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.081946757674871</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2335,7 +2352,7 @@
         <v>1432.250228548289</v>
       </c>
       <c r="E6">
-        <v>0.20221647827922684</v>
+        <v>-99.080090302739521</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2352,7 +2369,7 @@
         <v>1432.2798008874879</v>
       </c>
       <c r="E7">
-        <v>0.42281811421267124</v>
+        <v>-99.078065062268209</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2369,7 +2386,7 @@
         <v>1432.3263391617872</v>
       </c>
       <c r="E8">
-        <v>0.86845855014994056</v>
+        <v>-99.073973845796985</v>
       </c>
     </row>
   </sheetData>
@@ -2413,7 +2430,7 @@
         <v>1436.4648831013264</v>
       </c>
       <c r="E2">
-        <v>-0.52891942656348789</v>
+        <v>-99.084841101805509</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2430,7 +2447,7 @@
         <v>1436.4889090065249</v>
       </c>
       <c r="E3">
-        <v>-0.34772723346100209</v>
+        <v>-99.083174088168533</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2447,7 +2464,7 @@
         <v>1436.5049696335755</v>
       </c>
       <c r="E4">
-        <v>-0.19294397759184534</v>
+        <v>-99.081750043379984</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2464,7 +2481,7 @@
         <v>1436.5315962708696</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.079974910377231</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2481,7 +2498,7 @@
         <v>1436.5683629560774</v>
       </c>
       <c r="E6">
-        <v>0.31331488611544756</v>
+        <v>-99.077092334815433</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2498,7 +2515,7 @@
         <v>1436.5950858094307</v>
       </c>
       <c r="E7">
-        <v>0.61355108103155476</v>
+        <v>-99.074330086494086</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2515,7 +2532,7 @@
         <v>1436.6453087986272</v>
       </c>
       <c r="E8">
-        <v>1.1602075950696329</v>
+        <v>-99.069300709410882</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2576,7 @@
         <v>1431.6471949684803</v>
       </c>
       <c r="E2">
-        <v>-5.7849903064236784E-2</v>
+        <v>-99.058700120018827</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2576,7 +2593,7 @@
         <v>1431.6702632819695</v>
       </c>
       <c r="E3">
-        <v>-5.8952789314061414E-2</v>
+        <v>-99.058710507494922</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2593,7 +2610,7 @@
         <v>1431.6851136377836</v>
       </c>
       <c r="E4">
-        <v>-4.0325845655188708E-2</v>
+        <v>-99.058535070606553</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2610,7 +2627,7 @@
         <v>1431.7080366701609</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.058155263751914</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2627,7 +2644,7 @@
         <v>1431.7411383410299</v>
       </c>
       <c r="E6">
-        <v>9.9769728177555597E-2</v>
+        <v>-99.057215587818689</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2644,7 +2661,7 @@
         <v>1431.7646379894231</v>
       </c>
       <c r="E7">
-        <v>0.24803403925579906</v>
+        <v>-99.055819168209055</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2661,7 +2678,7 @@
         <v>1431.808451028963</v>
       </c>
       <c r="E8">
-        <v>0.62327080338880236</v>
+        <v>-99.052285020497621</v>
       </c>
     </row>
   </sheetData>
@@ -2705,7 +2722,7 @@
         <v>1430.5178783858944</v>
       </c>
       <c r="E2">
-        <v>-0.31061403762276718</v>
+        <v>-99.025621182570688</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2722,7 +2739,7 @@
         <v>1430.5308525981322</v>
       </c>
       <c r="E3">
-        <v>-0.20169574559027481</v>
+        <v>-99.024556599058982</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2739,7 +2756,7 @@
         <v>1430.5472687384126</v>
       </c>
       <c r="E4">
-        <v>-0.11609803149159707</v>
+        <v>-99.023719954328627</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2756,7 +2773,7 @@
         <v>1430.5653456938649</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.022585194980479</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2773,7 +2790,7 @@
         <v>1430.5882772098562</v>
       </c>
       <c r="E6">
-        <v>0.18659646104828187</v>
+        <v>-99.020761373544559</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2790,7 +2807,7 @@
         <v>1430.6141214294469</v>
       </c>
       <c r="E7">
-        <v>0.35863984489970901</v>
+        <v>-99.019079796039748</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2807,7 +2824,7 @@
         <v>1430.6508695943292</v>
       </c>
       <c r="E8">
-        <v>0.67888115956282069</v>
+        <v>-99.015949710018432</v>
       </c>
     </row>
   </sheetData>
@@ -2851,7 +2868,7 @@
         <v>1434.8660629667206</v>
       </c>
       <c r="E2">
-        <v>-2.4058102765219225E-3</v>
+        <v>-98.922342744114559</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2868,7 +2885,7 @@
         <v>1434.8891160010564</v>
       </c>
       <c r="E3">
-        <v>1.4554118380165162E-3</v>
+        <v>-98.922301132373178</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2885,7 +2902,7 @@
         <v>1434.9072394539751</v>
       </c>
       <c r="E4">
-        <v>-1.1737820717640727E-3</v>
+        <v>-98.92232946675378</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2902,7 +2919,7 @@
         <v>1434.9248518915999</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.922316817101802</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2919,7 +2936,7 @@
         <v>1434.958112777739</v>
       </c>
       <c r="E6">
-        <v>3.7616412583600335E-3</v>
+        <v>-98.922276278526553</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2936,7 +2953,7 @@
         <v>1434.98246365713</v>
       </c>
       <c r="E7">
-        <v>1.927604093146686E-2</v>
+        <v>-98.922109082450348</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2953,7 +2970,7 @@
         <v>1435.0191373471539</v>
       </c>
       <c r="E8">
-        <v>7.3726967157705894E-2</v>
+        <v>-98.921522273975469</v>
       </c>
     </row>
   </sheetData>
@@ -2997,7 +3014,7 @@
         <v>1434.4299954020144</v>
       </c>
       <c r="E2">
-        <v>8.6196159673367686E-3</v>
+        <v>-98.965851525349805</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3014,7 +3031,7 @@
         <v>1434.4522876859396</v>
       </c>
       <c r="E3">
-        <v>2.4390793069517616E-3</v>
+        <v>-98.965915435766576</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3031,7 +3048,7 @@
         <v>1434.4681470070955</v>
       </c>
       <c r="E4">
-        <v>7.1188065148994383E-3</v>
+        <v>-98.965867044610164</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3048,7 +3065,7 @@
         <v>1434.4977799198746</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.965940657294027</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3065,7 +3082,7 @@
         <v>1434.5328437089734</v>
       </c>
       <c r="E6">
-        <v>1.4086049577919467E-2</v>
+        <v>-98.96579499918235</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3082,7 +3099,7 @@
         <v>1434.5580989677285</v>
       </c>
       <c r="E7">
-        <v>5.6057817495023275E-2</v>
+        <v>-98.965360986194909</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -3099,7 +3116,7 @@
         <v>1434.611339861613</v>
       </c>
       <c r="E8">
-        <v>0.18214444193713189</v>
+        <v>-98.964057175674938</v>
       </c>
     </row>
   </sheetData>
@@ -3143,7 +3160,7 @@
         <v>1435.545645306516</v>
       </c>
       <c r="E2">
-        <v>-0.40503552825890249</v>
+        <v>-99.040079081174397</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3160,7 +3177,7 @@
         <v>1435.5662478916602</v>
       </c>
       <c r="E3">
-        <v>-0.28362010991231806</v>
+        <v>-99.038908849320251</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3177,7 +3194,7 @@
         <v>1435.5860524834247</v>
       </c>
       <c r="E4">
-        <v>-0.17223083922905444</v>
+        <v>-99.037835251958882</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3194,7 +3211,7 @@
         <v>1435.6078209182574</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.036175248500669</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3211,7 +3228,7 @@
         <v>1435.6377864213468</v>
       </c>
       <c r="E6">
-        <v>0.27428658320123156</v>
+        <v>-99.033531606521734</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3228,7 +3245,7 @@
         <v>1435.6655858380834</v>
       </c>
       <c r="E7">
-        <v>0.51556742327733385</v>
+        <v>-99.031206082064458</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -3245,7 +3262,7 @@
         <v>1435.7039438465399</v>
       </c>
       <c r="E8">
-        <v>0.96742773500776691</v>
+        <v>-99.026850940537798</v>
       </c>
     </row>
   </sheetData>
@@ -3289,7 +3306,7 @@
         <v>1432.306790914929</v>
       </c>
       <c r="E2">
-        <v>-0.44033847001788584</v>
+        <v>-99.046460192183147</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3306,7 +3323,7 @@
         <v>1432.326357528623</v>
       </c>
       <c r="E3">
-        <v>-0.30014040563115812</v>
+        <v>-99.045117435153671</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3323,7 +3340,7 @@
         <v>1432.3436382324096</v>
       </c>
       <c r="E4">
-        <v>-0.17600444641903928</v>
+        <v>-99.043928514089941</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3340,7 +3357,7 @@
         <v>1432.3638156044822</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.042242818865248</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3357,7 +3374,7 @@
         <v>1432.392868903182</v>
       </c>
       <c r="E6">
-        <v>0.29473439739332224</v>
+        <v>-99.039419979008954</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3374,7 +3391,7 @@
         <v>1432.4202932950604</v>
       </c>
       <c r="E7">
-        <v>0.55599876057608322</v>
+        <v>-99.036917700808814</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -3391,7 +3408,7 @@
         <v>1432.4596981237803</v>
       </c>
       <c r="E8">
-        <v>1.0036697735243743</v>
+        <v>-99.03263009953443</v>
       </c>
     </row>
   </sheetData>
@@ -3435,7 +3452,7 @@
         <v>1437.4951055703837</v>
       </c>
       <c r="E2">
-        <v>-0.31711920161582818</v>
+        <v>-98.993740816456381</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3452,7 +3469,7 @@
         <v>1437.5091152307955</v>
       </c>
       <c r="E3">
-        <v>-0.2059471170365903</v>
+        <v>-98.992618578313113</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3469,7 +3486,7 @@
         <v>1437.519114154898</v>
       </c>
       <c r="E4">
-        <v>-0.11270442417520084</v>
+        <v>-98.991677330274953</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3486,7 +3503,7 @@
         <v>1437.5402084771731</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.990539623770658</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3503,7 +3520,7 @@
         <v>1437.5652132396676</v>
       </c>
       <c r="E6">
-        <v>0.15764345195077545</v>
+        <v>-98.988948275587475</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3520,7 +3537,7 @@
         <v>1437.5834615278686</v>
       </c>
       <c r="E7">
-        <v>0.30327027085926977</v>
+        <v>-98.98747823055345</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -3537,7 +3554,7 @@
         <v>1437.6197663218281</v>
       </c>
       <c r="E8">
-        <v>0.60196490079647602</v>
+        <v>-98.984463026618315</v>
       </c>
     </row>
   </sheetData>
@@ -3581,7 +3598,7 @@
         <v>1449.8599918864134</v>
       </c>
       <c r="E2">
-        <v>-6.9985566925151926E-2</v>
+        <v>-99.242963171404966</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3598,7 +3615,7 @@
         <v>1449.8669924175254</v>
       </c>
       <c r="E3">
-        <v>-4.7763842819243132E-2</v>
+        <v>-99.242794826952718</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3615,7 +3632,7 @@
         <v>1449.8713466172512</v>
       </c>
       <c r="E4">
-        <v>-2.734736689517973E-2</v>
+        <v>-99.24264015846525</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3632,7 +3649,7 @@
         <v>1449.8730661628451</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.242432983833865</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3649,7 +3666,7 @@
         <v>1449.874389534534</v>
       </c>
       <c r="E6">
-        <v>4.3201677321069706E-2</v>
+        <v>-99.242105702176048</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3666,7 +3683,7 @@
         <v>1449.8721456917021</v>
       </c>
       <c r="E7">
-        <v>8.0754511393900649E-2</v>
+        <v>-99.241821214291491</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -3683,7 +3700,7 @@
         <v>1449.867065199312</v>
       </c>
       <c r="E8">
-        <v>0.14569715296516908</v>
+        <v>-99.24132923025951</v>
       </c>
     </row>
   </sheetData>
@@ -3727,7 +3744,7 @@
         <v>1432.8106943877413</v>
       </c>
       <c r="E2">
-        <v>-0.48477008417604517</v>
+        <v>-99.023218750440918</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3744,7 +3761,7 @@
         <v>1432.8274934456651</v>
       </c>
       <c r="E3">
-        <v>-0.32604839011981751</v>
+        <v>-99.021660834383425</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3761,7 +3778,7 @@
         <v>1432.8396891162238</v>
       </c>
       <c r="E4">
-        <v>-0.18273771549538048</v>
+        <v>-99.020254183562713</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3778,7 +3795,7 @@
         <v>1432.8613072362548</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.018460540778236</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3795,7 +3812,7 @@
         <v>1432.8909051088483</v>
       </c>
       <c r="E6">
-        <v>0.27629396296991721</v>
+        <v>-99.01574860650824</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3812,7 +3829,7 @@
         <v>1432.9130891121829</v>
       </c>
       <c r="E7">
-        <v>0.54834065030602019</v>
+        <v>-99.013078360924524</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -3829,7 +3846,7 @@
         <v>1432.951833290381</v>
       </c>
       <c r="E8">
-        <v>1.003471554512847</v>
+        <v>-99.008611071508625</v>
       </c>
     </row>
   </sheetData>
@@ -3873,7 +3890,7 @@
         <v>1433.0839297120601</v>
       </c>
       <c r="E2">
-        <v>-0.37866747566376308</v>
+        <v>-99.013660628256062</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3890,7 +3907,7 @@
         <v>1433.1026993335877</v>
       </c>
       <c r="E3">
-        <v>-0.25652465655339163</v>
+        <v>-99.012451306232251</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3907,7 +3924,7 @@
         <v>1433.1151700832145</v>
       </c>
       <c r="E4">
-        <v>-0.14539935341648388</v>
+        <v>-99.011351067368707</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3924,7 +3941,7 @@
         <v>1433.1399725609672</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.009911485069736</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3941,7 +3958,7 @@
         <v>1433.1699929199415</v>
       </c>
       <c r="E6">
-        <v>0.24210407763009814</v>
+        <v>-99.007514440402957</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3958,7 +3975,7 @@
         <v>1433.1915969485897</v>
       </c>
       <c r="E7">
-        <v>0.4734822825241804</v>
+        <v>-99.005223591370239</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -3975,7 +3992,7 @@
         <v>1433.234911961436</v>
       </c>
       <c r="E8">
-        <v>0.87001569857769534</v>
+        <v>-99.001297559560044</v>
       </c>
     </row>
   </sheetData>
@@ -4019,7 +4036,7 @@
         <v>1434.3034057306954</v>
       </c>
       <c r="E2">
-        <v>-0.40195979270602256</v>
+        <v>-99.017740232023613</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4036,7 +4053,7 @@
         <v>1434.3260487832974</v>
       </c>
       <c r="E3">
-        <v>-0.27398697434249736</v>
+        <v>-99.016478133385817</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4053,7 +4070,7 @@
         <v>1434.3409121188499</v>
       </c>
       <c r="E4">
-        <v>-0.15669847269862047</v>
+        <v>-99.015321406042887</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4070,7 +4087,7 @@
         <v>1434.3641771208179</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.013776008110199</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4087,7 +4104,7 @@
         <v>1434.3970896546257</v>
       </c>
       <c r="E6">
-        <v>0.24790555844318682</v>
+        <v>-99.011331104015611</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4104,7 +4121,7 @@
         <v>1434.4206658628257</v>
       </c>
       <c r="E7">
-        <v>0.49106503588066369</v>
+        <v>-99.008933006910567</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4121,7 +4138,7 @@
         <v>1434.4632879806588</v>
       </c>
       <c r="E8">
-        <v>0.90408965270546338</v>
+        <v>-99.004859659047014</v>
       </c>
     </row>
   </sheetData>
@@ -4165,7 +4182,7 @@
         <v>1436.7337316569071</v>
       </c>
       <c r="E2">
-        <v>-0.29800986081540326</v>
+        <v>-99.012101888477133</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4182,7 +4199,7 @@
         <v>1436.7480568202391</v>
       </c>
       <c r="E3">
-        <v>-0.1927327349201059</v>
+        <v>-99.011058749080291</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4199,7 +4216,7 @@
         <v>1436.7627163337731</v>
       </c>
       <c r="E4">
-        <v>-0.11013094145213806</v>
+        <v>-99.010240288429088</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4216,7 +4233,7 @@
         <v>1436.7843936822987</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.009149054954918</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4233,7 +4250,7 @@
         <v>1436.8099195644311</v>
       </c>
       <c r="E6">
-        <v>0.18871061017861193</v>
+        <v>-99.007279214090559</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4250,7 +4267,7 @@
         <v>1436.8305023527359</v>
       </c>
       <c r="E7">
-        <v>0.37167782710501313</v>
+        <v>-99.005466281692534</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4267,7 +4284,7 @@
         <v>1436.8714876782981</v>
       </c>
       <c r="E8">
-        <v>0.68436384000856798</v>
+        <v>-99.002368029378644</v>
       </c>
     </row>
   </sheetData>
@@ -4311,7 +4328,7 @@
         <v>1435.0354972578359</v>
       </c>
       <c r="E2">
-        <v>-0.30369722081961892</v>
+        <v>-99.005422930887391</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4328,7 +4345,7 @@
         <v>1435.0563126233758</v>
       </c>
       <c r="E3">
-        <v>-0.19814830704388484</v>
+        <v>-99.004369967774565</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4345,7 +4362,7 @@
         <v>1435.0724334368622</v>
       </c>
       <c r="E4">
-        <v>-0.10914976592171122</v>
+        <v>-99.003482112300318</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4362,7 +4379,7 @@
         <v>1435.0999022600568</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.002393226842585</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4379,7 +4396,7 @@
         <v>1435.1308001945838</v>
       </c>
       <c r="E6">
-        <v>0.18495796601886111</v>
+        <v>-99.000548073646087</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4396,7 +4413,7 @@
         <v>1435.1548514952312</v>
       </c>
       <c r="E7">
-        <v>0.3696853922717408</v>
+        <v>-98.99870522032991</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4413,7 +4430,7 @@
         <v>1435.2021718086414</v>
       </c>
       <c r="E8">
-        <v>0.69455346051128797</v>
+        <v>-98.995464314477317</v>
       </c>
     </row>
   </sheetData>
@@ -4457,7 +4474,7 @@
         <v>1441.0162279655594</v>
       </c>
       <c r="E2">
-        <v>-0.50527585396183916</v>
+        <v>-98.999250625660579</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4474,7 +4491,7 @@
         <v>1441.0308537168441</v>
       </c>
       <c r="E3">
-        <v>-0.33411364391253207</v>
+        <v>-98.997529022067141</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4491,7 +4508,7 @@
         <v>1441.0477611534093</v>
       </c>
       <c r="E4">
-        <v>-0.18972348023817268</v>
+        <v>-98.99607670017572</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4508,7 +4525,7 @@
         <v>1441.0662180607555</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.994168401461636</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4525,7 +4542,7 @@
         <v>1441.0909263581498</v>
       </c>
       <c r="E6">
-        <v>0.26027013657467801</v>
+        <v>-98.991550522186401</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4542,7 +4559,7 @@
         <v>1441.1177116451502</v>
       </c>
       <c r="E7">
-        <v>0.48855291853971394</v>
+        <v>-98.989254381831387</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4559,7 +4576,7 @@
         <v>1441.1556991474779</v>
       </c>
       <c r="E8">
-        <v>0.8989290595762035</v>
+        <v>-98.98512668893197</v>
       </c>
     </row>
   </sheetData>
@@ -4603,7 +4620,7 @@
         <v>1433.8570988482932</v>
       </c>
       <c r="E2">
-        <v>-0.26715863080861313</v>
+        <v>-98.991564928661148</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4620,7 +4637,7 @@
         <v>1433.8721575493639</v>
       </c>
       <c r="E3">
-        <v>-0.17413801455276801</v>
+        <v>-98.990624363341809</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4637,7 +4654,7 @@
         <v>1433.8927335795429</v>
       </c>
       <c r="E4">
-        <v>-0.10317641841620079</v>
+        <v>-98.989906844806512</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4654,7 +4671,7 @@
         <v>1433.9149342838448</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.988863590473841</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4671,7 +4688,7 @@
         <v>1433.9406332991741</v>
       </c>
       <c r="E6">
-        <v>0.16506365477157747</v>
+        <v>-98.987194571761563</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4688,7 +4705,7 @@
         <v>1433.9682985551337</v>
       </c>
       <c r="E7">
-        <v>0.32773535415872801</v>
+        <v>-98.985549738981064</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4705,7 +4722,7 @@
         <v>1434.0093064052335</v>
       </c>
       <c r="E8">
-        <v>0.64961888053859529</v>
+        <v>-98.982295057449562</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4766,7 @@
         <v>1430.7838161074251</v>
       </c>
       <c r="E2">
-        <v>-0.36204441364503409</v>
+        <v>-98.900857108379455</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4766,7 +4783,7 @@
         <v>1430.8038605901017</v>
       </c>
       <c r="E3">
-        <v>-0.26410748356632369</v>
+        <v>-98.899776730125097</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4783,7 +4800,7 @@
         <v>1430.8193553577582</v>
       </c>
       <c r="E4">
-        <v>-0.15971592575219107</v>
+        <v>-98.898625148500997</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4800,7 +4817,7 @@
         <v>1430.8439707981202</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.896863263449902</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4817,7 +4834,7 @@
         <v>1430.8806763048647</v>
       </c>
       <c r="E6">
-        <v>0.23761974830598734</v>
+        <v>-98.894241992713049</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4834,7 +4851,7 @@
         <v>1430.9082594901033</v>
       </c>
       <c r="E7">
-        <v>0.4472560427881721</v>
+        <v>-98.891929417735483</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4851,7 +4868,7 @@
         <v>1430.9537639810644</v>
       </c>
       <c r="E8">
-        <v>0.83484360512416067</v>
+        <v>-98.887653796949039</v>
       </c>
     </row>
   </sheetData>
@@ -4895,7 +4912,7 @@
         <v>1429.7040446107198</v>
       </c>
       <c r="E2">
-        <v>-0.15825466741141012</v>
+        <v>-98.931964272236044</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4912,7 +4929,7 @@
         <v>1429.728544535006</v>
       </c>
       <c r="E3">
-        <v>-0.11465961813542896</v>
+        <v>-98.931497923515622</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4929,7 +4946,7 @@
         <v>1429.7475142431886</v>
       </c>
       <c r="E4">
-        <v>-7.4119953926448254E-2</v>
+        <v>-98.931064259123815</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4946,7 +4963,7 @@
         <v>1429.7674934645111</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.930271376761141</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4963,7 +4980,7 @@
         <v>1429.8031261355584</v>
       </c>
       <c r="E6">
-        <v>0.15056876919185366</v>
+        <v>-98.928660699539435</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4980,7 +4997,7 @@
         <v>1429.8307765668635</v>
       </c>
       <c r="E7">
-        <v>0.3138883545207331</v>
+        <v>-98.926913623187801</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4997,7 +5014,7 @@
         <v>1429.8694213275101</v>
       </c>
       <c r="E8">
-        <v>0.62928866894948099</v>
+        <v>-98.923539695746584</v>
       </c>
     </row>
   </sheetData>
@@ -5041,7 +5058,7 @@
         <v>1438.5576423733619</v>
       </c>
       <c r="E2">
-        <v>-0.10848025139260105</v>
+        <v>-98.870734103186066</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5058,7 +5075,7 @@
         <v>1438.5764004299688</v>
       </c>
       <c r="E3">
-        <v>-8.4218333504277154E-2</v>
+        <v>-98.870459824082772</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5075,7 +5092,7 @@
         <v>1438.5991178528882</v>
       </c>
       <c r="E4">
-        <v>-5.5778333100125206E-2</v>
+        <v>-98.870138312080115</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5092,7 +5109,7 @@
         <v>1438.6246901623795</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.869507742342975</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5109,7 +5126,7 @@
         <v>1438.6541128000497</v>
       </c>
       <c r="E6">
-        <v>0.1139259652351188</v>
+        <v>-98.868219818126519</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5126,7 +5143,7 @@
         <v>1438.6839843615548</v>
       </c>
       <c r="E7">
-        <v>0.24333394058135585</v>
+        <v>-98.86675687098446</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5143,7 +5160,7 @@
         <v>1438.7292597131341</v>
       </c>
       <c r="E8">
-        <v>0.52682199581749234</v>
+        <v>-98.863552060468621</v>
       </c>
     </row>
   </sheetData>
@@ -5187,7 +5204,7 @@
         <v>1451.1393301651233</v>
       </c>
       <c r="E2">
-        <v>-6.4555777369701015E-2</v>
+        <v>-98.950226690928673</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5204,7 +5221,7 @@
         <v>1451.1400218675469</v>
       </c>
       <c r="E3">
-        <v>-4.4551842639826145E-2</v>
+        <v>-98.95001655930902</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5221,7 +5238,7 @@
         <v>1451.1375296217313</v>
       </c>
       <c r="E4">
-        <v>-2.6126077028999155E-2</v>
+        <v>-98.949823005589536</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5238,7 +5255,7 @@
         <v>1451.1326970383209</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.949548563838178</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5255,7 +5272,7 @@
         <v>1451.1226566321996</v>
       </c>
       <c r="E6">
-        <v>3.8879652333801147E-2</v>
+        <v>-98.949140151971847</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5272,7 +5289,7 @@
         <v>1451.1141383396912</v>
       </c>
       <c r="E7">
-        <v>7.2897528502116546E-2</v>
+        <v>-98.948782810703079</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5289,7 +5306,7 @@
         <v>1451.1027711937722</v>
       </c>
       <c r="E8">
-        <v>0.13157212912688401</v>
+        <v>-98.948166462518159</v>
       </c>
     </row>
   </sheetData>
@@ -5333,7 +5350,7 @@
         <v>1431.1020591621739</v>
       </c>
       <c r="E2">
-        <v>1.8355541368254215E-2</v>
+        <v>-98.201124105951038</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5350,7 +5367,7 @@
         <v>1431.1304302551157</v>
       </c>
       <c r="E3">
-        <v>1.3573771928664252E-2</v>
+        <v>-98.201210108262586</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5367,7 +5384,7 @@
         <v>1431.1534255720142</v>
       </c>
       <c r="E4">
-        <v>8.6057445767973705E-3</v>
+        <v>-98.201299460507954</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5384,7 +5401,7 @@
         <v>1431.189117287232</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.201454238762267</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5401,7 +5418,7 @@
         <v>1431.2275732292876</v>
       </c>
       <c r="E6">
-        <v>-6.0415072928024739E-3</v>
+        <v>-98.20156289803559</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5418,7 +5435,7 @@
         <v>1431.2635867720905</v>
       </c>
       <c r="E7">
-        <v>-8.7528267163965168E-3</v>
+        <v>-98.201611662356157</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5435,7 +5452,7 @@
         <v>1431.3207161507689</v>
       </c>
       <c r="E8">
-        <v>-7.6921706834830626E-3</v>
+        <v>-98.201592585972037</v>
       </c>
     </row>
   </sheetData>
@@ -5479,7 +5496,7 @@
         <v>1433.2245403794655</v>
       </c>
       <c r="E2">
-        <v>-0.24283463308689132</v>
+        <v>-98.809172818941221</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5496,7 +5513,7 @@
         <v>1433.2570233631297</v>
       </c>
       <c r="E3">
-        <v>-0.16478418830330824</v>
+        <v>-98.808241110519077</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5513,7 +5530,7 @@
         <v>1433.275273692743</v>
       </c>
       <c r="E4">
-        <v>-9.6290348107688814E-2</v>
+        <v>-98.807423481766875</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5530,7 +5547,7 @@
         <v>1433.308032585353</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.806274038883473</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5547,7 +5564,7 @@
         <v>1433.3486539146654</v>
       </c>
       <c r="E6">
-        <v>0.15704010212387154</v>
+        <v>-98.804399410415058</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5564,7 +5581,7 @@
         <v>1433.375443695259</v>
       </c>
       <c r="E7">
-        <v>0.31147101463407606</v>
+        <v>-98.802555928520434</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5581,7 +5598,7 @@
         <v>1433.4356548104029</v>
       </c>
       <c r="E8">
-        <v>0.59863521337333281</v>
+        <v>-98.79912797492905</v>
       </c>
     </row>
   </sheetData>
@@ -5625,7 +5642,7 @@
         <v>1436.3020667305022</v>
       </c>
       <c r="E2">
-        <v>-6.1009298858069327E-3</v>
+        <v>-98.776074993815712</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5642,7 +5659,7 @@
         <v>1436.3278636927205</v>
       </c>
       <c r="E3">
-        <v>-1.3009818425701378E-2</v>
+        <v>-98.776159558589427</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5659,7 +5676,7 @@
         <v>1436.3578226309808</v>
       </c>
       <c r="E4">
-        <v>-1.78293786865532E-2</v>
+        <v>-98.776218549991668</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5676,7 +5693,7 @@
         <v>1436.3882063021147</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.776000318453313</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5693,7 +5710,7 @@
         <v>1436.4262687112396</v>
       </c>
       <c r="E6">
-        <v>6.175282022001128E-2</v>
+        <v>-98.775244464130495</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5710,7 +5727,7 @@
         <v>1436.4637205431104</v>
       </c>
       <c r="E7">
-        <v>0.14646128090302774</v>
+        <v>-98.774207632841467</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5727,7 +5744,7 @@
         <v>1436.5131280206144</v>
       </c>
       <c r="E8">
-        <v>0.34906668090267257</v>
+        <v>-98.771727743390699</v>
       </c>
     </row>
   </sheetData>
@@ -5771,7 +5788,7 @@
         <v>1438.2347023433019</v>
       </c>
       <c r="E2">
-        <v>-0.25947386717714682</v>
+        <v>-98.744608983431007</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5788,7 +5805,7 @@
         <v>1438.2729887889245</v>
       </c>
       <c r="E3">
-        <v>-0.19052361706393811</v>
+        <v>-98.743741136348788</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5805,7 +5822,7 @@
         <v>1438.3095893299424</v>
       </c>
       <c r="E4">
-        <v>-0.12480442188666166</v>
+        <v>-98.742913957162557</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5822,7 +5839,7 @@
         <v>1438.3446882166968</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.741343097692095</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5839,7 +5856,7 @@
         <v>1438.4018550284475</v>
       </c>
       <c r="E6">
-        <v>0.22904449693064208</v>
+        <v>-98.738460213322142</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5856,7 +5873,7 @@
         <v>1438.4443682892693</v>
       </c>
       <c r="E7">
-        <v>0.4642910489598398</v>
+        <v>-98.735499266357564</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5873,7 +5890,7 @@
         <v>1438.5083025921679</v>
       </c>
       <c r="E8">
-        <v>0.90624140216461291</v>
+        <v>-98.729936627732187</v>
       </c>
     </row>
   </sheetData>
@@ -5917,7 +5934,7 @@
         <v>1435.4196054730926</v>
       </c>
       <c r="E2">
-        <v>-0.26476580691586987</v>
+        <v>-98.734593824524765</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5934,7 +5951,7 @@
         <v>1435.4558369280571</v>
       </c>
       <c r="E3">
-        <v>-0.18441018858166122</v>
+        <v>-98.733574300216262</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5951,7 +5968,7 @@
         <v>1435.4864539462665</v>
       </c>
       <c r="E4">
-        <v>-0.11955567233105326</v>
+        <v>-98.732751448532639</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5968,7 +5985,7 @@
         <v>1435.5154701943814</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.731234567489508</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5985,7 +6002,7 @@
         <v>1435.5700109109853</v>
       </c>
       <c r="E6">
-        <v>0.11737032542388352</v>
+        <v>-98.729745413372498</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6002,7 +6019,7 @@
         <v>1435.6078397881163</v>
       </c>
       <c r="E7">
-        <v>0.23513412738751346</v>
+        <v>-98.728251266961166</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6019,7 +6036,7 @@
         <v>1435.6676910228557</v>
       </c>
       <c r="E8">
-        <v>0.50190451062587293</v>
+        <v>-98.724866576554476</v>
       </c>
     </row>
   </sheetData>
@@ -6063,7 +6080,7 @@
         <v>1438.0083788592767</v>
       </c>
       <c r="E2">
-        <v>-7.9574076389884577E-2</v>
+        <v>-98.561591118173936</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6080,7 +6097,7 @@
         <v>1438.0470106819166</v>
       </c>
       <c r="E3">
-        <v>-6.8187125926319647E-2</v>
+        <v>-98.561427196828205</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6097,7 +6114,7 @@
         <v>1438.0773240027088</v>
       </c>
       <c r="E4">
-        <v>-4.4792295750685766E-2</v>
+        <v>-98.561090415522457</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6114,7 +6131,7 @@
         <v>1438.1209046582649</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.56044560606081</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6131,7 +6148,7 @@
         <v>1438.1663827192067</v>
       </c>
       <c r="E6">
-        <v>0.10092422428457071</v>
+        <v>-98.558992746955596</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6148,7 +6165,7 @@
         <v>1438.2115650027124</v>
       </c>
       <c r="E7">
-        <v>0.21181836580695118</v>
+        <v>-98.557396365468676</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6165,7 +6182,7 @@
         <v>1438.277030537658</v>
       </c>
       <c r="E8">
-        <v>0.45901461223191797</v>
+        <v>-98.553837841041613</v>
       </c>
     </row>
   </sheetData>
@@ -6209,7 +6226,7 @@
         <v>1437.6903084032756</v>
       </c>
       <c r="E2">
-        <v>-6.1362843577151514E-2</v>
+        <v>-98.583845005217441</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6226,7 +6243,7 @@
         <v>1437.7287355586261</v>
       </c>
       <c r="E3">
-        <v>-4.6086789167622967E-2</v>
+        <v>-98.583628539780563</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6243,7 +6260,7 @@
         <v>1437.7517985583602</v>
       </c>
       <c r="E4">
-        <v>-2.5131754535620159E-2</v>
+        <v>-98.58333160180139</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6260,7 +6277,7 @@
         <v>1437.7966512551625</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.582975478676971</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6277,7 +6294,7 @@
         <v>1437.8464155595457</v>
       </c>
       <c r="E6">
-        <v>6.5314326255374741E-2</v>
+        <v>-98.582049958658004</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6294,7 +6311,7 @@
         <v>1437.8835633769445</v>
       </c>
       <c r="E7">
-        <v>0.14450623273571034</v>
+        <v>-98.58092778992426</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6311,7 +6328,7 @@
         <v>1437.9564504649925</v>
       </c>
       <c r="E8">
-        <v>0.31953661593555377</v>
+        <v>-98.578447566474551</v>
       </c>
     </row>
   </sheetData>
@@ -6355,7 +6372,7 @@
         <v>1438.9180501436372</v>
       </c>
       <c r="E2">
-        <v>-0.11737433095767937</v>
+        <v>-98.658159303075763</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6372,7 +6389,7 @@
         <v>1438.9619357188899</v>
       </c>
       <c r="E3">
-        <v>-0.10092177755479613</v>
+        <v>-98.657938276590144</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6389,7 +6406,7 @@
         <v>1438.9973390109735</v>
       </c>
       <c r="E4">
-        <v>-7.0190373176385795E-2</v>
+        <v>-98.657525425518273</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6406,7 +6423,7 @@
         <v>1439.0310336702566</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.656582475744685</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6423,7 +6440,7 @@
         <v>1439.0923701902191</v>
       </c>
       <c r="E6">
-        <v>0.13212966700162451</v>
+        <v>-98.654807422643444</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6440,7 +6457,7 @@
         <v>1439.1335216551313</v>
       </c>
       <c r="E7">
-        <v>0.28260023387218991</v>
+        <v>-98.652785974679261</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6457,7 +6474,7 @@
         <v>1439.2004714301415</v>
       </c>
       <c r="E8">
-        <v>0.59017146501072437</v>
+        <v>-98.648654008860575</v>
       </c>
     </row>
   </sheetData>
@@ -6501,7 +6518,7 @@
         <v>1439.5926801576904</v>
       </c>
       <c r="E2">
-        <v>2.5915099908380812E-2</v>
+        <v>-98.368584433400699</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6518,7 +6535,7 @@
         <v>1439.6291794193826</v>
       </c>
       <c r="E3">
-        <v>9.0987465297887801E-3</v>
+        <v>-98.368858706929203</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6535,7 +6552,7 @@
         <v>1439.6619544465977</v>
       </c>
       <c r="E4">
-        <v>2.7326981894015725E-3</v>
+        <v>-98.368962536725192</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6552,7 +6569,7 @@
         <v>1439.7062626699592</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.369007106838467</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6569,7 +6586,7 @@
         <v>1439.7541348515042</v>
       </c>
       <c r="E6">
-        <v>3.0870473958033752E-2</v>
+        <v>-98.368503611602108</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6586,7 +6603,7 @@
         <v>1439.8026291978997</v>
       </c>
       <c r="E7">
-        <v>7.6485403016830919E-2</v>
+        <v>-98.36775963535095</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6603,7 +6620,7 @@
         <v>1439.8701510852131</v>
       </c>
       <c r="E8">
-        <v>0.19161090882895204</v>
+        <v>-98.365881946532951</v>
       </c>
     </row>
   </sheetData>
@@ -6647,7 +6664,7 @@
         <v>1447.3945446720495</v>
       </c>
       <c r="E2">
-        <v>-0.13607108320617761</v>
+        <v>-97.432554204090408</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6664,7 +6681,7 @@
         <v>1447.4213951398522</v>
       </c>
       <c r="E3">
-        <v>-8.7036793919883976E-2</v>
+        <v>-97.431293559919382</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6681,7 +6698,7 @@
         <v>1447.4420499835812</v>
       </c>
       <c r="E4">
-        <v>-4.4448933341820256E-2</v>
+        <v>-97.430198649827389</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6698,7 +6715,7 @@
         <v>1447.4593831716381</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-97.429055892594846</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6715,7 +6732,7 @@
         <v>1447.488191124035</v>
       </c>
       <c r="E6">
-        <v>7.3769072604901967E-2</v>
+        <v>-97.427159330969616</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6732,7 +6749,7 @@
         <v>1447.5049845892247</v>
       </c>
       <c r="E7">
-        <v>0.12445984911585506</v>
+        <v>-97.425856099437908</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6749,7 +6766,7 @@
         <v>1447.530009669345</v>
       </c>
       <c r="E8">
-        <v>0.20679206243383191</v>
+        <v>-97.423739384251121</v>
       </c>
     </row>
   </sheetData>
@@ -6793,7 +6810,7 @@
         <v>1441.9219688812136</v>
       </c>
       <c r="E2">
-        <v>-0.63712037694226198</v>
+        <v>-99.341486344108134</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6810,7 +6827,7 @@
         <v>1441.9156320802417</v>
       </c>
       <c r="E3">
-        <v>-0.36880704041511708</v>
+        <v>-99.339708134812781</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6827,7 +6844,7 @@
         <v>1441.9128801670024</v>
       </c>
       <c r="E4">
-        <v>-0.19135832962691271</v>
+        <v>-99.338532118178406</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6844,7 +6861,7 @@
         <v>1441.9089144920738</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.337263917481053</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6861,7 +6878,7 @@
         <v>1441.9068254772649</v>
       </c>
       <c r="E6">
-        <v>0.22842078352105075</v>
+        <v>-99.335750090528691</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6878,7 +6895,7 @@
         <v>1441.9090164401998</v>
       </c>
       <c r="E7">
-        <v>0.39132276053229048</v>
+        <v>-99.33467048034791</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6895,7 +6912,7 @@
         <v>1441.9213816053043</v>
       </c>
       <c r="E8">
-        <v>0.62955194134906978</v>
+        <v>-99.333091649607553</v>
       </c>
     </row>
   </sheetData>
@@ -7051,7 +7068,7 @@
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA7A15B-0C6D-452E-9D40-CF074EA64640}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -7085,25 +7102,25 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>242.2</v>
+        <v>1.48</v>
       </c>
       <c r="B2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="C2">
-        <v>113.753388492073</v>
+        <v>33729.862157679105</v>
       </c>
       <c r="D2">
-        <v>-18.633758627701685</v>
+        <v>-99.523602674809254</v>
       </c>
       <c r="E2">
-        <v>41.741352574135156</v>
+        <v>-99.515230083738729</v>
       </c>
       <c r="F2">
-        <v>41.741352574135156</v>
+        <v>99.523602674809254</v>
       </c>
       <c r="G2">
-        <v>58.024449111202259</v>
+        <v>2.8569991582468153</v>
       </c>
       <c r="H2">
         <v>0.3</v>
@@ -7114,25 +7131,25 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>30.4</v>
+        <v>1.49</v>
       </c>
       <c r="B3">
         <v>1E-4</v>
       </c>
       <c r="C3">
-        <v>84.210113234573726</v>
+        <v>32911.73237563741</v>
       </c>
       <c r="D3">
-        <v>-0.54420697764468362</v>
+        <v>-98.880277999022042</v>
       </c>
       <c r="E3">
-        <v>1.072170447364309</v>
+        <v>-98.878576353892157</v>
       </c>
       <c r="F3">
-        <v>1.072170447364309</v>
+        <v>98.880277999022042</v>
       </c>
       <c r="G3">
-        <v>1.3681318512663005</v>
+        <v>0.58033913652597213</v>
       </c>
       <c r="H3">
         <v>0.3</v>
@@ -7143,25 +7160,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>59.55</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="B4">
         <v>1E-4</v>
       </c>
       <c r="C4">
-        <v>76.801713118660189</v>
+        <v>29958.989693409567</v>
       </c>
       <c r="D4">
-        <v>-0.58803869091894012</v>
+        <v>-99.242963171404966</v>
       </c>
       <c r="E4">
-        <v>1.0733124320621066</v>
+        <v>-99.24132923025951</v>
       </c>
       <c r="F4">
-        <v>1.0733124320621066</v>
+        <v>99.242963171404966</v>
       </c>
       <c r="G4">
-        <v>1.2419782860989677</v>
+        <v>0.48374919903720864</v>
       </c>
       <c r="H4">
         <v>0.3</v>
@@ -7172,25 +7189,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>94.52</v>
+        <v>4.53</v>
       </c>
       <c r="B5">
         <v>1E-4</v>
       </c>
       <c r="C5">
-        <v>76.088814272539608</v>
+        <v>22293.097943774603</v>
       </c>
       <c r="D5">
-        <v>-0.31061403762276718</v>
+        <v>-98.950226690928673</v>
       </c>
       <c r="E5">
-        <v>0.67888115956282069</v>
+        <v>-98.948166462518159</v>
       </c>
       <c r="F5">
-        <v>0.67888115956282069</v>
+        <v>98.950226690928673</v>
       </c>
       <c r="G5">
-        <v>0.69583495066420131</v>
+        <v>0.45991644856850711</v>
       </c>
       <c r="H5">
         <v>0.3</v>
@@ -7201,25 +7218,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>129.52000000000001</v>
+        <v>7.57</v>
       </c>
       <c r="B6">
         <v>1E-4</v>
       </c>
       <c r="C6">
-        <v>75.22083337994313</v>
+        <v>17864.487144254166</v>
       </c>
       <c r="D6">
-        <v>-0.10848025139260105</v>
+        <v>-99.341486344108134</v>
       </c>
       <c r="E6">
-        <v>0.52682199581749234</v>
+        <v>-99.333091649607553</v>
       </c>
       <c r="F6">
-        <v>0.52682199581749234</v>
+        <v>99.341486344108134</v>
       </c>
       <c r="G6">
-        <v>0.38566647334663218</v>
+        <v>1.5015261438626415</v>
       </c>
       <c r="H6">
         <v>0.3</v>
@@ -7230,25 +7247,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>159.5</v>
+        <v>8.49</v>
       </c>
       <c r="B7">
         <v>1E-4</v>
       </c>
       <c r="C7">
-        <v>69.583856725239158</v>
+        <v>17188.559224123157</v>
       </c>
       <c r="D7">
-        <v>-0.25947386717714682</v>
+        <v>-99.373523464328187</v>
       </c>
       <c r="E7">
-        <v>0.90624140216461291</v>
+        <v>-99.364462969680432</v>
       </c>
       <c r="F7">
-        <v>0.90624140216461291</v>
+        <v>99.373523464328187</v>
       </c>
       <c r="G7">
-        <v>0.74388751952898868</v>
+        <v>1.523745086732466</v>
       </c>
       <c r="H7">
         <v>0.3</v>
@@ -7259,25 +7276,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>189.58</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="B8">
         <v>1E-4</v>
       </c>
       <c r="C8">
-        <v>179.58112542944616</v>
+        <v>16605.694075207102</v>
       </c>
       <c r="D8">
-        <v>-0.13607108320617761</v>
+        <v>-99.378503510504586</v>
       </c>
       <c r="E8">
-        <v>0.20679206243383191</v>
+        <v>-99.367454444316039</v>
       </c>
       <c r="F8">
-        <v>0.20679206243383191</v>
+        <v>99.378503510504586</v>
       </c>
       <c r="G8">
-        <v>0.64139448582722769</v>
+        <v>1.8386767368512771</v>
       </c>
       <c r="H8">
         <v>0.3</v>
@@ -7288,25 +7305,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>219.71</v>
+        <v>10.42</v>
       </c>
       <c r="B9">
         <v>1E-4</v>
       </c>
       <c r="C9">
-        <v>68.955594609671166</v>
+        <v>16152.535299755002</v>
       </c>
       <c r="D9">
-        <v>-9.5365289721715846E-2</v>
+        <v>-99.373594312633315</v>
       </c>
       <c r="E9">
-        <v>0.48796116700832948</v>
+        <v>-99.364317944861241</v>
       </c>
       <c r="F9">
-        <v>0.48796116700832948</v>
+        <v>99.373594312633315</v>
       </c>
       <c r="G9">
-        <v>0.34172980249437246</v>
+        <v>1.5092963934334855</v>
       </c>
       <c r="H9">
         <v>0.3</v>
@@ -7317,28 +7334,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>249.61</v>
+        <v>14.53</v>
       </c>
       <c r="B10">
         <v>1E-4</v>
       </c>
       <c r="C10">
-        <v>68.911757018421014</v>
+        <v>14601.549470215145</v>
       </c>
       <c r="D10">
-        <v>-1.9375385176094571E-2</v>
+        <v>-99.364839997246079</v>
       </c>
       <c r="E10">
-        <v>0.31887972275065041</v>
+        <v>-99.352291403789209</v>
       </c>
       <c r="F10">
-        <v>0.31887972275065041</v>
+        <v>99.364839997246079</v>
       </c>
       <c r="G10">
-        <v>0.15105014029714786</v>
+        <v>1.7857853153103622</v>
       </c>
       <c r="H10">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="I10">
         <v>3</v>
@@ -7346,30 +7363,1741 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
+        <v>15.41</v>
+      </c>
+      <c r="B11">
+        <v>1E-4</v>
+      </c>
+      <c r="C11">
+        <v>14385.20376780466</v>
+      </c>
+      <c r="D11">
+        <v>-99.362112237434928</v>
+      </c>
+      <c r="E11">
+        <v>-99.352824071229961</v>
+      </c>
+      <c r="F11">
+        <v>99.362112237434928</v>
+      </c>
+      <c r="G11">
+        <v>1.253596165163452</v>
+      </c>
+      <c r="H11">
+        <v>0.3</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="B12">
+        <v>1E-4</v>
+      </c>
+      <c r="C12">
+        <v>13470.55741836318</v>
+      </c>
+      <c r="D12">
+        <v>-99.335223322480687</v>
+      </c>
+      <c r="E12">
+        <v>-99.327458696976862</v>
+      </c>
+      <c r="F12">
+        <v>99.335223322480687</v>
+      </c>
+      <c r="G12">
+        <v>0.94127910098259759</v>
+      </c>
+      <c r="H12">
+        <v>0.3</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>20.38</v>
+      </c>
+      <c r="B13">
+        <v>1E-4</v>
+      </c>
+      <c r="C13">
+        <v>13282.769241017102</v>
+      </c>
+      <c r="D13">
+        <v>-99.332126038868466</v>
+      </c>
+      <c r="E13">
+        <v>-99.324063229474376</v>
+      </c>
+      <c r="F13">
+        <v>99.332126038868466</v>
+      </c>
+      <c r="G13">
+        <v>0.92359014754091007</v>
+      </c>
+      <c r="H13">
+        <v>0.3</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>29.52</v>
+      </c>
+      <c r="B14">
+        <v>1E-4</v>
+      </c>
+      <c r="C14">
+        <v>11950.463643098708</v>
+      </c>
+      <c r="D14">
+        <v>-99.283916762275609</v>
+      </c>
+      <c r="E14">
+        <v>-99.276047336374774</v>
+      </c>
+      <c r="F14">
+        <v>99.283916762275609</v>
+      </c>
+      <c r="G14">
+        <v>0.81679668750544543</v>
+      </c>
+      <c r="H14">
+        <v>0.3</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>30.4</v>
+      </c>
+      <c r="B15">
+        <v>1E-4</v>
+      </c>
+      <c r="C15">
+        <v>11822.226852050338</v>
+      </c>
+      <c r="D15">
+        <v>-99.29157309387999</v>
+      </c>
+      <c r="E15">
+        <v>-99.280059583972474</v>
+      </c>
+      <c r="F15">
+        <v>99.29157309387999</v>
+      </c>
+      <c r="G15">
+        <v>1.3681318512663005</v>
+      </c>
+      <c r="H15">
+        <v>0.3</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>39.520000000000003</v>
+      </c>
+      <c r="B16">
+        <v>1E-4</v>
+      </c>
+      <c r="C16">
+        <v>10908.03603041542</v>
+      </c>
+      <c r="D16">
+        <v>-99.237504348887654</v>
+      </c>
+      <c r="E16">
+        <v>-99.226351594897139</v>
+      </c>
+      <c r="F16">
+        <v>99.237504348887654</v>
+      </c>
+      <c r="G16">
+        <v>1.0954375161859222</v>
+      </c>
+      <c r="H16">
+        <v>0.3</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>40.43</v>
+      </c>
+      <c r="B17">
+        <v>1E-4</v>
+      </c>
+      <c r="C17">
+        <v>10716.760681504378</v>
+      </c>
+      <c r="D17">
+        <v>-99.249525538593801</v>
+      </c>
+      <c r="E17">
+        <v>-99.236456461300108</v>
+      </c>
+      <c r="F17">
+        <v>99.249525538593801</v>
+      </c>
+      <c r="G17">
+        <v>1.3016439548174432</v>
+      </c>
+      <c r="H17">
+        <v>0.3</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>49.57</v>
+      </c>
+      <c r="B18">
+        <v>1E-4</v>
+      </c>
+      <c r="C18">
+        <v>10137.523261343951</v>
+      </c>
+      <c r="D18">
+        <v>-99.217290586795713</v>
+      </c>
+      <c r="E18">
+        <v>-99.210836175987225</v>
+      </c>
+      <c r="F18">
+        <v>99.217290586795713</v>
+      </c>
+      <c r="G18">
+        <v>0.48326416907055203</v>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>59.55</v>
+      </c>
+      <c r="B19">
+        <v>1E-4</v>
+      </c>
+      <c r="C19">
+        <v>9411.0459558780894</v>
+      </c>
+      <c r="D19">
+        <v>-99.188718345567679</v>
+      </c>
+      <c r="E19">
+        <v>-99.175160382623417</v>
+      </c>
+      <c r="F19">
+        <v>99.188718345567679</v>
+      </c>
+      <c r="G19">
+        <v>1.2419782860989677</v>
+      </c>
+      <c r="H19">
+        <v>0.3</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>69.53</v>
+      </c>
+      <c r="B20">
+        <v>1E-4</v>
+      </c>
+      <c r="C20">
+        <v>8778.6838772800293</v>
+      </c>
+      <c r="D20">
+        <v>-99.139082429856529</v>
+      </c>
+      <c r="E20">
+        <v>-99.126772262009951</v>
+      </c>
+      <c r="F20">
+        <v>99.139082429856529</v>
+      </c>
+      <c r="G20">
+        <v>1.0550843620601424</v>
+      </c>
+      <c r="H20">
+        <v>0.3</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>79.58</v>
+      </c>
+      <c r="B21">
+        <v>1E-4</v>
+      </c>
+      <c r="C21">
+        <v>8286.4793234824047</v>
+      </c>
+      <c r="D21">
+        <v>-99.088649927712353</v>
+      </c>
+      <c r="E21">
+        <v>-99.075549844538742</v>
+      </c>
+      <c r="F21">
+        <v>99.088649927712353</v>
+      </c>
+      <c r="G21">
+        <v>0.93832584093397764</v>
+      </c>
+      <c r="H21">
+        <v>0.3</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>84.52</v>
+      </c>
+      <c r="B22">
+        <v>1E-4</v>
+      </c>
+      <c r="C22">
+        <v>8026.353206922533</v>
+      </c>
+      <c r="D22">
+        <v>-99.084657420933425</v>
+      </c>
+      <c r="E22">
+        <v>-99.073973845796985</v>
+      </c>
+      <c r="F22">
+        <v>99.084657420933425</v>
+      </c>
+      <c r="G22">
+        <v>0.69647763895753634</v>
+      </c>
+      <c r="H22">
+        <v>0.3</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>85.49</v>
+      </c>
+      <c r="B23">
+        <v>1E-4</v>
+      </c>
+      <c r="C23">
+        <v>8017.3228143353954</v>
+      </c>
+      <c r="D23">
+        <v>-99.084841101805509</v>
+      </c>
+      <c r="E23">
+        <v>-99.069300709410882</v>
+      </c>
+      <c r="F23">
+        <v>99.084841101805509</v>
+      </c>
+      <c r="G23">
+        <v>1.1281908809252212</v>
+      </c>
+      <c r="H23">
+        <v>0.3</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>89.51</v>
+      </c>
+      <c r="B24">
+        <v>1E-4</v>
+      </c>
+      <c r="C24">
+        <v>7932.7702609818407</v>
+      </c>
+      <c r="D24">
+        <v>-99.058710507494922</v>
+      </c>
+      <c r="E24">
+        <v>-99.052285020497621</v>
+      </c>
+      <c r="F24">
+        <v>99.058710507494922</v>
+      </c>
+      <c r="G24">
+        <v>0.31623469053924647</v>
+      </c>
+      <c r="H24">
+        <v>0.5</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>94.52</v>
+      </c>
+      <c r="B25">
+        <v>1E-4</v>
+      </c>
+      <c r="C25">
+        <v>7784.7004037370598</v>
+      </c>
+      <c r="D25">
+        <v>-99.025621182570688</v>
+      </c>
+      <c r="E25">
+        <v>-99.015949710018432</v>
+      </c>
+      <c r="F25">
+        <v>99.025621182570688</v>
+      </c>
+      <c r="G25">
+        <v>0.69583495066420131</v>
+      </c>
+      <c r="H25">
+        <v>0.3</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>95.47</v>
+      </c>
+      <c r="B26">
+        <v>1E-4</v>
+      </c>
+      <c r="C26">
+        <v>7679.9644676022172</v>
+      </c>
+      <c r="D26">
+        <v>-98.922342744114559</v>
+      </c>
+      <c r="E26">
+        <v>-98.921522273975469</v>
+      </c>
+      <c r="F26">
+        <v>98.922342744114559</v>
+      </c>
+      <c r="G26">
+        <v>1.2341149961671573E-2</v>
+      </c>
+      <c r="H26">
+        <v>0.3</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>96.55</v>
+      </c>
+      <c r="B27">
+        <v>1E-4</v>
+      </c>
+      <c r="C27">
+        <v>7600.0166338135214</v>
+      </c>
+      <c r="D27">
+        <v>-98.965940657294027</v>
+      </c>
+      <c r="E27">
+        <v>-98.964057175674938</v>
+      </c>
+      <c r="F27">
+        <v>98.965940657294027</v>
+      </c>
+      <c r="G27">
+        <v>1.6542527711733864E-2</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>97.46</v>
+      </c>
+      <c r="B28">
+        <v>1E-4</v>
+      </c>
+      <c r="C28">
+        <v>7873.7446479669643</v>
+      </c>
+      <c r="D28">
+        <v>-99.040079081174397</v>
+      </c>
+      <c r="E28">
+        <v>-99.026850940537798</v>
+      </c>
+      <c r="F28">
+        <v>99.040079081174397</v>
+      </c>
+      <c r="G28">
+        <v>1.0237613122577807</v>
+      </c>
+      <c r="H28">
+        <v>0.3</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>99.52</v>
+      </c>
+      <c r="B29">
+        <v>1E-4</v>
+      </c>
+      <c r="C29">
+        <v>7772.2572676779637</v>
+      </c>
+      <c r="D29">
+        <v>-99.046460192183147</v>
+      </c>
+      <c r="E29">
+        <v>-99.03263009953443</v>
+      </c>
+      <c r="F29">
+        <v>99.046460192183147</v>
+      </c>
+      <c r="G29">
+        <v>1.0586771128240415</v>
+      </c>
+      <c r="H29">
+        <v>0.3</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>100.44</v>
+      </c>
+      <c r="B30">
+        <v>1E-4</v>
+      </c>
+      <c r="C30">
+        <v>7727.1993054024288</v>
+      </c>
+      <c r="D30">
+        <v>-98.993740816456381</v>
+      </c>
+      <c r="E30">
+        <v>-98.984463026618315</v>
+      </c>
+      <c r="F30">
+        <v>98.993740816456381</v>
+      </c>
+      <c r="G30">
+        <v>0.63711122380362362</v>
+      </c>
+      <c r="H30">
+        <v>0.3</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>101.52</v>
+      </c>
+      <c r="B31">
+        <v>1E-4</v>
+      </c>
+      <c r="C31">
+        <v>7619.2556850833298</v>
+      </c>
+      <c r="D31">
+        <v>-99.023218750440918</v>
+      </c>
+      <c r="E31">
+        <v>-99.008611071508625</v>
+      </c>
+      <c r="F31">
+        <v>99.023218750440918</v>
+      </c>
+      <c r="G31">
+        <v>1.0371554947932662</v>
+      </c>
+      <c r="H31">
+        <v>0.3</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>102.57</v>
+      </c>
+      <c r="B32">
+        <v>1E-4</v>
+      </c>
+      <c r="C32">
+        <v>7582.3371598120893</v>
+      </c>
+      <c r="D32">
+        <v>-99.013660628256062</v>
+      </c>
+      <c r="E32">
+        <v>-99.001297559560044</v>
+      </c>
+      <c r="F32">
+        <v>99.013660628256062</v>
+      </c>
+      <c r="G32">
+        <v>0.87888807193734653</v>
+      </c>
+      <c r="H32">
+        <v>0.3</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>104.55</v>
+      </c>
+      <c r="B33">
+        <v>1E-4</v>
+      </c>
+      <c r="C33">
+        <v>7506.2881192408031</v>
+      </c>
+      <c r="D33">
+        <v>-99.017740232023613</v>
+      </c>
+      <c r="E33">
+        <v>-99.004859659047014</v>
+      </c>
+      <c r="F33">
+        <v>99.017740232023613</v>
+      </c>
+      <c r="G33">
+        <v>0.90492357475634988</v>
+      </c>
+      <c r="H33">
+        <v>0.3</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>105.44</v>
+      </c>
+      <c r="B34">
+        <v>1E-4</v>
+      </c>
+      <c r="C34">
+        <v>7473.7036855491042</v>
+      </c>
+      <c r="D34">
+        <v>-99.012101888477133</v>
+      </c>
+      <c r="E34">
+        <v>-99.002368029378644</v>
+      </c>
+      <c r="F34">
+        <v>99.012101888477133</v>
+      </c>
+      <c r="G34">
+        <v>0.66859956409612009</v>
+      </c>
+      <c r="H34">
+        <v>0.3</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>107.5</v>
+      </c>
+      <c r="B35">
+        <v>1E-4</v>
+      </c>
+      <c r="C35">
+        <v>7386.7989408224748</v>
+      </c>
+      <c r="D35">
+        <v>-99.005422930887391</v>
+      </c>
+      <c r="E35">
+        <v>-98.995464314477317</v>
+      </c>
+      <c r="F35">
+        <v>99.005422930887391</v>
+      </c>
+      <c r="G35">
+        <v>0.65479146932623611</v>
+      </c>
+      <c r="H35">
+        <v>0.3</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>108.41</v>
+      </c>
+      <c r="B36">
+        <v>1E-4</v>
+      </c>
+      <c r="C36">
+        <v>7345.1939022722681</v>
+      </c>
+      <c r="D36">
+        <v>-98.999250625660579</v>
+      </c>
+      <c r="E36">
+        <v>-98.98512668893197</v>
+      </c>
+      <c r="F36">
+        <v>98.999250625660579</v>
+      </c>
+      <c r="G36">
+        <v>1.0044210290456956</v>
+      </c>
+      <c r="H36">
+        <v>0.3</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>109.52</v>
+      </c>
+      <c r="B37">
+        <v>1E-4</v>
+      </c>
+      <c r="C37">
+        <v>7320.5634554022981</v>
+      </c>
+      <c r="D37">
+        <v>-98.991564928661148</v>
+      </c>
+      <c r="E37">
+        <v>-98.982295057449562</v>
+      </c>
+      <c r="F37">
+        <v>98.991564928661148</v>
+      </c>
+      <c r="G37">
+        <v>0.59987231736564361</v>
+      </c>
+      <c r="H37">
+        <v>0.3</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>119.57</v>
+      </c>
+      <c r="B38">
+        <v>1E-4</v>
+      </c>
+      <c r="C38">
+        <v>6948.9673854643597</v>
+      </c>
+      <c r="D38">
+        <v>-98.900857108379455</v>
+      </c>
+      <c r="E38">
+        <v>-98.887653796949039</v>
+      </c>
+      <c r="F38">
+        <v>98.900857108379455</v>
+      </c>
+      <c r="G38">
+        <v>0.92021240507935209</v>
+      </c>
+      <c r="H38">
+        <v>0.3</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>120.45</v>
+      </c>
+      <c r="B39">
+        <v>1E-4</v>
+      </c>
+      <c r="C39">
+        <v>6937.6887133173441</v>
+      </c>
+      <c r="D39">
+        <v>-98.931964272236044</v>
+      </c>
+      <c r="E39">
+        <v>-98.923539695746584</v>
+      </c>
+      <c r="F39">
+        <v>98.931964272236044</v>
+      </c>
+      <c r="G39">
+        <v>0.50379123320639019</v>
+      </c>
+      <c r="H39">
+        <v>0.3</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>129.52000000000001</v>
+      </c>
+      <c r="B40">
+        <v>1E-4</v>
+      </c>
+      <c r="C40">
+        <v>6653.8123432919856</v>
+      </c>
+      <c r="D40">
+        <v>-98.870734103186066</v>
+      </c>
+      <c r="E40">
+        <v>-98.863552060468621</v>
+      </c>
+      <c r="F40">
+        <v>98.870734103186066</v>
+      </c>
+      <c r="G40">
+        <v>0.38566647334663218</v>
+      </c>
+      <c r="H40">
+        <v>0.3</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>139.54</v>
+      </c>
+      <c r="B41">
+        <v>1E-4</v>
+      </c>
+      <c r="C41">
+        <v>6151.6437544044475</v>
+      </c>
+      <c r="D41">
+        <v>-98.201611662356157</v>
+      </c>
+      <c r="E41">
+        <v>-98.201124105951038</v>
+      </c>
+      <c r="F41">
+        <v>98.201611662356157</v>
+      </c>
+      <c r="G41">
+        <v>-4.8960937213953254E-2</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>140.46</v>
+      </c>
+      <c r="B42">
+        <v>1E-4</v>
+      </c>
+      <c r="C42">
+        <v>6002.6473874954318</v>
+      </c>
+      <c r="D42">
+        <v>-98.809172818941221</v>
+      </c>
+      <c r="E42">
+        <v>-98.79912797492905</v>
+      </c>
+      <c r="F42">
+        <v>98.809172818941221</v>
+      </c>
+      <c r="G42">
+        <v>0.54842313846240254</v>
+      </c>
+      <c r="H42">
+        <v>0.3</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>149.57</v>
+      </c>
+      <c r="B43">
+        <v>1E-4</v>
+      </c>
+      <c r="C43">
+        <v>6034.3938138616877</v>
+      </c>
+      <c r="D43">
+        <v>-98.776218549991668</v>
+      </c>
+      <c r="E43">
+        <v>-98.771727743390699</v>
+      </c>
+      <c r="F43">
+        <v>98.776218549991668</v>
+      </c>
+      <c r="G43">
+        <v>0.17758725426227992</v>
+      </c>
+      <c r="H43">
+        <v>0.7</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>159.5</v>
+      </c>
+      <c r="B44">
+        <v>1E-4</v>
+      </c>
+      <c r="C44">
+        <v>5528.4213352859515</v>
+      </c>
+      <c r="D44">
+        <v>-98.744608983431007</v>
+      </c>
+      <c r="E44">
+        <v>-98.729936627732187</v>
+      </c>
+      <c r="F44">
+        <v>98.744608983431007</v>
+      </c>
+      <c r="G44">
+        <v>0.74388751952898868</v>
+      </c>
+      <c r="H44">
+        <v>0.3</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>160.36000000000001</v>
+      </c>
+      <c r="B45">
+        <v>1E-4</v>
+      </c>
+      <c r="C45">
+        <v>5526.8607689274504</v>
+      </c>
+      <c r="D45">
+        <v>-98.734593824524765</v>
+      </c>
+      <c r="E45">
+        <v>-98.724866576554476</v>
+      </c>
+      <c r="F45">
+        <v>98.734593824524765</v>
+      </c>
+      <c r="G45">
+        <v>0.50194193841004109</v>
+      </c>
+      <c r="H45">
+        <v>0.3</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>169.55</v>
+      </c>
+      <c r="B46">
+        <v>1E-4</v>
+      </c>
+      <c r="C46">
+        <v>5540.1967191394597</v>
+      </c>
+      <c r="D46">
+        <v>-98.561591118173936</v>
+      </c>
+      <c r="E46">
+        <v>-98.553837841041613</v>
+      </c>
+      <c r="F46">
+        <v>98.561591118173936</v>
+      </c>
+      <c r="G46">
+        <v>0.3511098065885388</v>
+      </c>
+      <c r="H46">
+        <v>0.3</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>170.4</v>
+      </c>
+      <c r="B47">
+        <v>1E-4</v>
+      </c>
+      <c r="C47">
+        <v>5360.6084371690495</v>
+      </c>
+      <c r="D47">
+        <v>-98.583845005217441</v>
+      </c>
+      <c r="E47">
+        <v>-98.578447566474551</v>
+      </c>
+      <c r="F47">
+        <v>98.583845005217441</v>
+      </c>
+      <c r="G47">
+        <v>0.20756881569239855</v>
+      </c>
+      <c r="H47">
+        <v>0.3</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>179.5</v>
+      </c>
+      <c r="B48">
+        <v>1E-4</v>
+      </c>
+      <c r="C48">
+        <v>5235.7033203326355</v>
+      </c>
+      <c r="D48">
+        <v>-98.658159303075763</v>
+      </c>
+      <c r="E48">
+        <v>-98.648654008860575</v>
+      </c>
+      <c r="F48">
+        <v>98.658159303075763</v>
+      </c>
+      <c r="G48">
+        <v>0.42993801255636749</v>
+      </c>
+      <c r="H48">
+        <v>0.3</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>180.09</v>
+      </c>
+      <c r="B49">
+        <v>1E-4</v>
+      </c>
+      <c r="C49">
+        <v>5323.7485046317952</v>
+      </c>
+      <c r="D49">
+        <v>-98.369007106838467</v>
+      </c>
+      <c r="E49">
+        <v>-98.365881946532951</v>
+      </c>
+      <c r="F49">
+        <v>98.369007106838467</v>
+      </c>
+      <c r="G49">
+        <v>7.3814259543183547E-2</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>189.58</v>
+      </c>
+      <c r="B50">
+        <v>1E-4</v>
+      </c>
+      <c r="C50">
+        <v>6985.0264310372813</v>
+      </c>
+      <c r="D50">
+        <v>-97.432554204090408</v>
+      </c>
+      <c r="E50">
+        <v>-97.423739384251121</v>
+      </c>
+      <c r="F50">
+        <v>97.432554204090408</v>
+      </c>
+      <c r="G50">
+        <v>0.64139448582722769</v>
+      </c>
+      <c r="H50">
+        <v>0.3</v>
+      </c>
+      <c r="I50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>190.44</v>
+      </c>
+      <c r="B51">
+        <v>1E-4</v>
+      </c>
+      <c r="C51">
+        <v>7108.0869273352555</v>
+      </c>
+      <c r="D51">
+        <v>-97.47359279896385</v>
+      </c>
+      <c r="E51">
+        <v>-97.463214180208013</v>
+      </c>
+      <c r="F51">
+        <v>97.47359279896385</v>
+      </c>
+      <c r="G51">
+        <v>0.74735684796979485</v>
+      </c>
+      <c r="H51">
+        <v>0.3</v>
+      </c>
+      <c r="I51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>199.6</v>
+      </c>
+      <c r="B52">
+        <v>1E-4</v>
+      </c>
+      <c r="C52">
+        <v>5813.9817511847259</v>
+      </c>
+      <c r="D52">
+        <v>-98.155411240437047</v>
+      </c>
+      <c r="E52">
+        <v>-98.154115605772873</v>
+      </c>
+      <c r="F52">
+        <v>98.155411240437047</v>
+      </c>
+      <c r="G52">
+        <v>7.4236119915604817E-2</v>
+      </c>
+      <c r="H52">
+        <v>0.3</v>
+      </c>
+      <c r="I52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>200.36</v>
+      </c>
+      <c r="B53">
+        <v>1E-4</v>
+      </c>
+      <c r="C53">
+        <v>5587.244259223201</v>
+      </c>
+      <c r="D53">
+        <v>-98.274232380258823</v>
+      </c>
+      <c r="E53">
+        <v>-98.270096071490499</v>
+      </c>
+      <c r="F53">
+        <v>98.274232380258823</v>
+      </c>
+      <c r="G53">
+        <v>0.22801332716436248</v>
+      </c>
+      <c r="H53">
+        <v>0.3</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>209.57</v>
+      </c>
+      <c r="B54">
+        <v>1E-4</v>
+      </c>
+      <c r="C54">
+        <v>5378.9134239449522</v>
+      </c>
+      <c r="D54">
+        <v>-97.634126559316272</v>
+      </c>
+      <c r="E54">
+        <v>-97.623055612446208</v>
+      </c>
+      <c r="F54">
+        <v>97.634126559316272</v>
+      </c>
+      <c r="G54">
+        <v>0.5930643339793773</v>
+      </c>
+      <c r="H54">
+        <v>0.3</v>
+      </c>
+      <c r="I54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>210.11</v>
+      </c>
+      <c r="B55">
+        <v>1E-4</v>
+      </c>
+      <c r="C55">
+        <v>5605.1649225643732</v>
+      </c>
+      <c r="D55">
+        <v>-97.965733856596557</v>
+      </c>
+      <c r="E55">
+        <v>-97.965056023487449</v>
+      </c>
+      <c r="F55">
+        <v>97.965733856596557</v>
+      </c>
+      <c r="G55">
+        <v>-3.4302197950485856E-2</v>
+      </c>
+      <c r="H55">
+        <v>1.5</v>
+      </c>
+      <c r="I55">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>219.71</v>
+      </c>
+      <c r="B56">
+        <v>1E-4</v>
+      </c>
+      <c r="C56">
+        <v>4459.8377064849519</v>
+      </c>
+      <c r="D56">
+        <v>-98.455328659002078</v>
+      </c>
+      <c r="E56">
+        <v>-98.446309581330965</v>
+      </c>
+      <c r="F56">
+        <v>98.455328659002078</v>
+      </c>
+      <c r="G56">
+        <v>0.34172980249437246</v>
+      </c>
+      <c r="H56">
+        <v>0.3</v>
+      </c>
+      <c r="I56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>229.52</v>
+      </c>
+      <c r="B57">
+        <v>1E-4</v>
+      </c>
+      <c r="C57">
+        <v>4471.305974908656</v>
+      </c>
+      <c r="D57">
+        <v>-98.340541995996091</v>
+      </c>
+      <c r="E57">
+        <v>-98.336809903779908</v>
+      </c>
+      <c r="F57">
+        <v>98.340541995996091</v>
+      </c>
+      <c r="G57">
+        <v>0.10166762529520101</v>
+      </c>
+      <c r="H57">
+        <v>0.3</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>230.16</v>
+      </c>
+      <c r="B58">
+        <v>1E-4</v>
+      </c>
+      <c r="C58">
+        <v>4511.9915392946741</v>
+      </c>
+      <c r="D58">
+        <v>-98.461054788977137</v>
+      </c>
+      <c r="E58">
+        <v>-98.454406059227281</v>
+      </c>
+      <c r="F58">
+        <v>98.461054788977137</v>
+      </c>
+      <c r="G58">
+        <v>0.2438171971423452</v>
+      </c>
+      <c r="H58">
+        <v>0.3</v>
+      </c>
+      <c r="I58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>236.53</v>
+      </c>
+      <c r="B59">
+        <v>1E-4</v>
+      </c>
+      <c r="C59">
+        <v>4288.5363931878874</v>
+      </c>
+      <c r="D59">
+        <v>-98.398742014732932</v>
+      </c>
+      <c r="E59">
+        <v>-98.390746839801068</v>
+      </c>
+      <c r="F59">
+        <v>98.398742014732932</v>
+      </c>
+      <c r="G59">
+        <v>0.28333075855816636</v>
+      </c>
+      <c r="H59">
+        <v>0.3</v>
+      </c>
+      <c r="I59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>239.94</v>
+      </c>
+      <c r="B60">
+        <v>1E-4</v>
+      </c>
+      <c r="C60">
+        <v>4277.3484813683508</v>
+      </c>
+      <c r="D60">
+        <v>-98.420032201881156</v>
+      </c>
+      <c r="E60">
+        <v>-98.409678047710969</v>
+      </c>
+      <c r="F60">
+        <v>98.420032201881156</v>
+      </c>
+      <c r="G60">
+        <v>0.37295179140445095</v>
+      </c>
+      <c r="H60">
+        <v>0.3</v>
+      </c>
+      <c r="I60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>249.61</v>
+      </c>
+      <c r="B61">
+        <v>1E-4</v>
+      </c>
+      <c r="C61">
+        <v>4131.4108759593119</v>
+      </c>
+      <c r="D61">
+        <v>-98.33232745014574</v>
+      </c>
+      <c r="E61">
+        <v>-98.326685369387476</v>
+      </c>
+      <c r="F61">
+        <v>98.33232745014574</v>
+      </c>
+      <c r="G61">
+        <v>0.15105014029714786</v>
+      </c>
+      <c r="H61">
+        <v>0.7</v>
+      </c>
+      <c r="I61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>250.31</v>
+      </c>
+      <c r="B62">
+        <v>1E-4</v>
+      </c>
+      <c r="C62">
+        <v>4117.7409326731886</v>
+      </c>
+      <c r="D62">
+        <v>-98.338808369736995</v>
+      </c>
+      <c r="E62">
+        <v>-98.330695194905303</v>
+      </c>
+      <c r="F62">
+        <v>98.338808369736995</v>
+      </c>
+      <c r="G62">
+        <v>0.28907583319986957</v>
+      </c>
+      <c r="H62">
+        <v>0.3</v>
+      </c>
+      <c r="I62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>259.52</v>
+      </c>
+      <c r="B63">
+        <v>1E-4</v>
+      </c>
+      <c r="C63">
+        <v>3920.8683203777728</v>
+      </c>
+      <c r="D63">
+        <v>-98.292959226782671</v>
+      </c>
+      <c r="E63">
+        <v>-98.281139684062367</v>
+      </c>
+      <c r="F63">
+        <v>98.292959226782671</v>
+      </c>
+      <c r="G63">
+        <v>0.38556932733492516</v>
+      </c>
+      <c r="H63">
+        <v>0.3</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>260.27</v>
+      </c>
+      <c r="B64">
+        <v>1E-4</v>
+      </c>
+      <c r="C64">
+        <v>3920.2652841771264</v>
+      </c>
+      <c r="D64">
+        <v>-98.282648609963459</v>
+      </c>
+      <c r="E64">
+        <v>-98.275788651849979</v>
+      </c>
+      <c r="F64">
+        <v>98.282648609963459</v>
+      </c>
+      <c r="G64">
+        <v>0.18198113719698944</v>
+      </c>
+      <c r="H64">
+        <v>0.3</v>
+      </c>
+      <c r="I64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>269.64</v>
+      </c>
+      <c r="B65">
+        <v>1E-4</v>
+      </c>
+      <c r="C65">
+        <v>3814.112122481456</v>
+      </c>
+      <c r="D65">
+        <v>-98.229621157144777</v>
+      </c>
+      <c r="E65">
+        <v>-98.224980123870793</v>
+      </c>
+      <c r="F65">
+        <v>98.229621157144777</v>
+      </c>
+      <c r="G65">
+        <v>9.9716443971796201E-2</v>
+      </c>
+      <c r="H65">
+        <v>0.7</v>
+      </c>
+      <c r="I65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>270.27</v>
+      </c>
+      <c r="B66">
+        <v>1E-4</v>
+      </c>
+      <c r="C66">
+        <v>3802.0568800097376</v>
+      </c>
+      <c r="D66">
+        <v>-98.226050090016969</v>
+      </c>
+      <c r="E66">
+        <v>-98.220076834680327</v>
+      </c>
+      <c r="F66">
+        <v>98.226050090016969</v>
+      </c>
+      <c r="G66">
+        <v>0.15626257697928742</v>
+      </c>
+      <c r="H66">
+        <v>0.5</v>
+      </c>
+      <c r="I66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>279.61</v>
+      </c>
+      <c r="B67">
+        <v>1E-4</v>
+      </c>
+      <c r="C67">
+        <v>3694.0245637708458</v>
+      </c>
+      <c r="D67">
+        <v>-98.180534527484255</v>
+      </c>
+      <c r="E67">
+        <v>-98.174199224750723</v>
+      </c>
+      <c r="F67">
+        <v>98.180534527484255</v>
+      </c>
+      <c r="G67">
+        <v>0.18225712680152106</v>
+      </c>
+      <c r="H67">
+        <v>0.5</v>
+      </c>
+      <c r="I67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68">
         <v>280.33999999999997</v>
       </c>
-      <c r="B11">
-        <v>1E-4</v>
-      </c>
-      <c r="C11">
-        <v>67.083028629233141</v>
-      </c>
-      <c r="D11">
-        <v>-1.5475239982848096E-2</v>
-      </c>
-      <c r="E11">
-        <v>0.26845305433424982</v>
-      </c>
-      <c r="F11">
-        <v>0.26845305433424982</v>
-      </c>
-      <c r="G11">
+      <c r="B68">
+        <v>1E-4</v>
+      </c>
+      <c r="C68">
+        <v>3665.9631312670294</v>
+      </c>
+      <c r="D68">
+        <v>-98.1703949284841</v>
+      </c>
+      <c r="E68">
+        <v>-98.16519935798479</v>
+      </c>
+      <c r="F68">
+        <v>98.1703949284841</v>
+      </c>
+      <c r="G68">
         <v>0.11934897733253454</v>
       </c>
-      <c r="H11">
+      <c r="H68">
         <v>0.5</v>
       </c>
-      <c r="I11">
+      <c r="I68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>284.42</v>
+      </c>
+      <c r="B69">
+        <v>1E-4</v>
+      </c>
+      <c r="C69">
+        <v>3679.5277339786448</v>
+      </c>
+      <c r="D69">
+        <v>-98.183465011223859</v>
+      </c>
+      <c r="E69">
+        <v>-98.178635331039374</v>
+      </c>
+      <c r="F69">
+        <v>98.183465011223859</v>
+      </c>
+      <c r="G69">
+        <v>0.10373699800013608</v>
+      </c>
+      <c r="H69">
+        <v>0.5</v>
+      </c>
+      <c r="I69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>280.49</v>
+      </c>
+      <c r="B70">
+        <v>1E-4</v>
+      </c>
+      <c r="C70">
+        <v>3669.532851562094</v>
+      </c>
+      <c r="D70">
+        <v>-98.180663392340861</v>
+      </c>
+      <c r="E70">
+        <v>-98.175697240607164</v>
+      </c>
+      <c r="F70">
+        <v>98.180663392340861</v>
+      </c>
+      <c r="G70">
+        <v>0.11010865439994486</v>
+      </c>
+      <c r="H70">
+        <v>0.5</v>
+      </c>
+      <c r="I70">
         <v>3</v>
       </c>
     </row>
@@ -7560,7 +9288,7 @@
         <v>1422.1925333324789</v>
       </c>
       <c r="E2">
-        <v>-9.5365289721715846E-2</v>
+        <v>-98.455328659002078</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7577,7 +9305,7 @@
         <v>1422.2283278845616</v>
       </c>
       <c r="E3">
-        <v>-7.3976608519859016E-2</v>
+        <v>-98.454997958800121</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -7594,7 +9322,7 @@
         <v>1422.2702066069942</v>
       </c>
       <c r="E4">
-        <v>-5.4251597716371947E-2</v>
+        <v>-98.454692981368623</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -7611,7 +9339,7 @@
         <v>1422.3094976369466</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.453854172554202</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -7628,7 +9356,7 @@
         <v>1422.3732047435167</v>
       </c>
       <c r="E6">
-        <v>0.10978186180242767</v>
+        <v>-98.452156784878653</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -7645,7 +9373,7 @@
         <v>1422.4207845887968</v>
       </c>
       <c r="E7">
-        <v>0.23392407497864881</v>
+        <v>-98.450237365229526</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -7662,7 +9390,7 @@
         <v>1422.4908743867375</v>
       </c>
       <c r="E8">
-        <v>0.48796116700832948</v>
+        <v>-98.446309581330965</v>
       </c>
     </row>
   </sheetData>
@@ -7706,7 +9434,7 @@
         <v>1413.8577641515244</v>
       </c>
       <c r="E2">
-        <v>-4.6500616115784793E-3</v>
+        <v>-98.332081832377384</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7723,7 +9451,7 @@
         <v>1413.9071293683758</v>
       </c>
       <c r="E3">
-        <v>-1.877986437305049E-2</v>
+        <v>-98.33231751688416</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -7740,7 +9468,7 @@
         <v>1413.9443569434318</v>
       </c>
       <c r="E4">
-        <v>-1.9375385176094571E-2</v>
+        <v>-98.33232745014574</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -7757,7 +9485,7 @@
         <v>1413.9871736685664</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.332004269548236</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -7774,7 +9502,7 @@
         <v>1414.0604102964714</v>
       </c>
       <c r="E6">
-        <v>5.3176200121965694E-2</v>
+        <v>-98.331117292800585</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -7791,7 +9519,7 @@
         <v>1414.1041901361909</v>
       </c>
       <c r="E7">
-        <v>0.13297791788855037</v>
+        <v>-98.329786203555429</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -7808,7 +9536,7 @@
         <v>1414.1909737395545</v>
       </c>
       <c r="E8">
-        <v>0.31887972275065041</v>
+        <v>-98.326685369387476</v>
       </c>
     </row>
   </sheetData>
@@ -7852,7 +9580,7 @@
         <v>1406.8081200445693</v>
       </c>
       <c r="E2">
-        <v>-1.0959609158214484E-2</v>
+        <v>-98.170312297486163</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7869,7 +9597,7 @@
         <v>1406.8459476408925</v>
       </c>
       <c r="E3">
-        <v>-1.5475239982848096E-2</v>
+        <v>-98.1703949284841</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -7886,7 +9614,7 @@
         <v>1406.8733028175316</v>
       </c>
       <c r="E4">
-        <v>-9.7636607225206271E-3</v>
+        <v>-98.170290412966253</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -7903,7 +9631,7 @@
         <v>1406.9277007538108</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-98.170111748885816</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -7920,7 +9648,7 @@
         <v>1406.9822644993521</v>
       </c>
       <c r="E6">
-        <v>4.9124113135952503E-2</v>
+        <v>-98.169212832511079</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -7937,7 +9665,7 @@
         <v>1407.0429923936567</v>
       </c>
       <c r="E7">
-        <v>0.11264722100411526</v>
+        <v>-98.168050430623452</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -7954,7 +9682,591 @@
         <v>1407.125456118496</v>
       </c>
       <c r="E8">
-        <v>0.26845305433424982</v>
+        <v>-98.16519935798479</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58D0784B-A472-4F65-BB90-913D0BBC6F46}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>179.57921998810818</v>
+      </c>
+      <c r="D2">
+        <v>1444.0839241779122</v>
+      </c>
+      <c r="E2">
+        <v>-97.47359279896385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>179.66086417724989</v>
+      </c>
+      <c r="D3">
+        <v>1444.0796095694543</v>
+      </c>
+      <c r="E3">
+        <v>-97.47244418907799</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>179.735080886378</v>
+      </c>
+      <c r="D4">
+        <v>1444.077227395441</v>
+      </c>
+      <c r="E4">
+        <v>-97.471400072568343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>179.84403478359457</v>
+      </c>
+      <c r="D5">
+        <v>1444.0714207880569</v>
+      </c>
+      <c r="E5">
+        <v>-97.469867256519095</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>179.98245093526018</v>
+      </c>
+      <c r="D6">
+        <v>1444.0565005519195</v>
+      </c>
+      <c r="E6">
+        <v>-97.467919951244411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>180.11360299815436</v>
+      </c>
+      <c r="D7">
+        <v>1444.0464247569685</v>
+      </c>
+      <c r="E7">
+        <v>-97.466074840679013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>180.31694123112862</v>
+      </c>
+      <c r="D8">
+        <v>1444.0293391324876</v>
+      </c>
+      <c r="E8">
+        <v>-97.463214180208013</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E32DDC1-0436-47CF-B8B8-7827E4CC656D}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>107.24405386539478</v>
+      </c>
+      <c r="D2">
+        <v>1442.6721580277069</v>
+      </c>
+      <c r="E2">
+        <v>-98.155411240437047</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>107.25626319949534</v>
+      </c>
+      <c r="D3">
+        <v>1442.6819462723022</v>
+      </c>
+      <c r="E3">
+        <v>-98.155201240911367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>107.26441303801376</v>
+      </c>
+      <c r="D4">
+        <v>1442.6908300446441</v>
+      </c>
+      <c r="E4">
+        <v>-98.155061064370273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>107.27318768125413</v>
+      </c>
+      <c r="D5">
+        <v>1442.701760950898</v>
+      </c>
+      <c r="E5">
+        <v>-98.154910141240208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>107.28898469031377</v>
+      </c>
+      <c r="D6">
+        <v>1442.7058662249315</v>
+      </c>
+      <c r="E6">
+        <v>-98.154638434005207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>107.29878427080394</v>
+      </c>
+      <c r="D7">
+        <v>1442.7178862695423</v>
+      </c>
+      <c r="E7">
+        <v>-98.154469882040146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>107.31938182833197</v>
+      </c>
+      <c r="D8">
+        <v>1442.7312186877855</v>
+      </c>
+      <c r="E8">
+        <v>-98.154115605772873</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3252D777-AA3F-429A-AB84-23D0D2B2F124}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>96.422852261520902</v>
+      </c>
+      <c r="D2">
+        <v>1433.3639326045623</v>
+      </c>
+      <c r="E2">
+        <v>-98.274232380258823</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>96.459030765949095</v>
+      </c>
+      <c r="D3">
+        <v>1433.3931357526938</v>
+      </c>
+      <c r="E3">
+        <v>-98.273584860609617</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>96.478792504581662</v>
+      </c>
+      <c r="D4">
+        <v>1433.4186603318747</v>
+      </c>
+      <c r="E4">
+        <v>-98.273231166772092</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>96.509798736763713</v>
+      </c>
+      <c r="D5">
+        <v>1433.450799835246</v>
+      </c>
+      <c r="E5">
+        <v>-98.272676219990771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>96.55426336972414</v>
+      </c>
+      <c r="D6">
+        <v>1433.4834656871226</v>
+      </c>
+      <c r="E6">
+        <v>-98.271880395951257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>96.585583228418244</v>
+      </c>
+      <c r="D7">
+        <v>1433.5182258053417</v>
+      </c>
+      <c r="E7">
+        <v>-98.27131983591056</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>96.653957935724108</v>
+      </c>
+      <c r="D8">
+        <v>1433.5654055221305</v>
+      </c>
+      <c r="E8">
+        <v>-98.270096071490499</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33117070-9DAC-44DF-871B-9807CB16C8B4}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>127.25828409448513</v>
+      </c>
+      <c r="D2">
+        <v>1441.9489418629778</v>
+      </c>
+      <c r="E2">
+        <v>-97.634126559316272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>127.29049310967174</v>
+      </c>
+      <c r="D3">
+        <v>1441.9818652655219</v>
+      </c>
+      <c r="E3">
+        <v>-97.633527757799172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>127.32886554825768</v>
+      </c>
+      <c r="D4">
+        <v>1442.0238051914471</v>
+      </c>
+      <c r="E4">
+        <v>-97.632814371366592</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>127.41263750937229</v>
+      </c>
+      <c r="D5">
+        <v>1442.0675639801959</v>
+      </c>
+      <c r="E5">
+        <v>-97.631256957173221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>127.52516582126017</v>
+      </c>
+      <c r="D6">
+        <v>1442.1253945207989</v>
+      </c>
+      <c r="E6">
+        <v>-97.629164930345141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>127.65964321030786</v>
+      </c>
+      <c r="D7">
+        <v>1442.167271786213</v>
+      </c>
+      <c r="E7">
+        <v>-97.626664845691423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>127.85378074183654</v>
+      </c>
+      <c r="D8">
+        <v>1442.2260437616544</v>
+      </c>
+      <c r="E8">
+        <v>-97.623055612446208</v>
       </c>
     </row>
   </sheetData>
@@ -7998,7 +10310,7 @@
         <v>1436.9025034802239</v>
       </c>
       <c r="E2">
-        <v>-0.60850024545834247</v>
+        <v>-99.373523464328187</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8015,7 +10327,7 @@
         <v>1436.8911568632095</v>
       </c>
       <c r="E3">
-        <v>-0.3702879457555292</v>
+        <v>-99.372021983651848</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -8032,7 +10344,7 @@
         <v>1436.8863246997562</v>
       </c>
       <c r="E4">
-        <v>-0.20281256752158155</v>
+        <v>-99.370966366269826</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -8049,7 +10361,7 @@
         <v>1436.8819621817163</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.369688014348327</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -8066,7 +10378,7 @@
         <v>1436.8800363205162</v>
       </c>
       <c r="E6">
-        <v>0.26270532117561896</v>
+        <v>-99.368032151222025</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -8083,7 +10395,7 @@
         <v>1436.883018592727</v>
       </c>
       <c r="E7">
-        <v>0.48237945628811851</v>
+        <v>-99.366647518819022</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -8100,7 +10412,1467 @@
         <v>1436.8960977763741</v>
       </c>
       <c r="E8">
-        <v>0.82896165499696783</v>
+        <v>-99.364462969680432</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8B24A4-9675-4A1B-9BC6-260F154F35E0}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>114.06196596531714</v>
+      </c>
+      <c r="D2">
+        <v>1433.1654272740338</v>
+      </c>
+      <c r="E2">
+        <v>-97.965056023487449</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>114.0436505080112</v>
+      </c>
+      <c r="D3">
+        <v>1433.1993710380523</v>
+      </c>
+      <c r="E3">
+        <v>-97.965382783851496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>114.03532609657236</v>
+      </c>
+      <c r="D4">
+        <v>1433.2216610871844</v>
+      </c>
+      <c r="E4">
+        <v>-97.965531297080901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>114.02557282863192</v>
+      </c>
+      <c r="D5">
+        <v>1433.259221689937</v>
+      </c>
+      <c r="E5">
+        <v>-97.965705302093681</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>114.02397230165253</v>
+      </c>
+      <c r="D6">
+        <v>1433.3038012656882</v>
+      </c>
+      <c r="E6">
+        <v>-97.965733856596557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>114.03410172276692</v>
+      </c>
+      <c r="D7">
+        <v>1433.3337251027381</v>
+      </c>
+      <c r="E7">
+        <v>-97.965553140752263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>114.05389630567691</v>
+      </c>
+      <c r="D8">
+        <v>1433.3953425079169</v>
+      </c>
+      <c r="E8">
+        <v>-97.965199991769438</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69F8CD83-B7B6-48BE-B95D-7DC3133EB49F}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>74.199444884126819</v>
+      </c>
+      <c r="D2">
+        <v>1430.4208973096704</v>
+      </c>
+      <c r="E2">
+        <v>-98.340541995996091</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>74.203462150695316</v>
+      </c>
+      <c r="D3">
+        <v>1430.4681800420326</v>
+      </c>
+      <c r="E3">
+        <v>-98.340452150510416</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>74.211385409436389</v>
+      </c>
+      <c r="D4">
+        <v>1430.4991670004276</v>
+      </c>
+      <c r="E4">
+        <v>-98.340274948172109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>74.222967240122657</v>
+      </c>
+      <c r="D5">
+        <v>1430.5397607123991</v>
+      </c>
+      <c r="E5">
+        <v>-98.340015922492555</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>74.245036704005145</v>
+      </c>
+      <c r="D6">
+        <v>1430.6002395966525</v>
+      </c>
+      <c r="E6">
+        <v>-98.339522342674783</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>74.284626545826171</v>
+      </c>
+      <c r="D7">
+        <v>1430.6372282683219</v>
+      </c>
+      <c r="E7">
+        <v>-98.338636922575077</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>74.366318146378347</v>
+      </c>
+      <c r="D8">
+        <v>1430.7168167971759</v>
+      </c>
+      <c r="E8">
+        <v>-98.336809903779908</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3A4CB6-A4F7-407C-882D-B5F398CC921A}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>69.437077715731661</v>
+      </c>
+      <c r="D2">
+        <v>1422.1271244424609</v>
+      </c>
+      <c r="E2">
+        <v>-98.461054788977137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>69.438951742535536</v>
+      </c>
+      <c r="D3">
+        <v>1422.1768009714494</v>
+      </c>
+      <c r="E3">
+        <v>-98.461013254617271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>69.448325749583319</v>
+      </c>
+      <c r="D4">
+        <v>1422.2150219818427</v>
+      </c>
+      <c r="E4">
+        <v>-98.46080549697929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>69.475887031596969</v>
+      </c>
+      <c r="D5">
+        <v>1422.2518939928475</v>
+      </c>
+      <c r="E5">
+        <v>-98.460194651817588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>69.529027588523121</v>
+      </c>
+      <c r="D6">
+        <v>1422.3201068430099</v>
+      </c>
+      <c r="E6">
+        <v>-98.459016889038949</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>69.596883240904617</v>
+      </c>
+      <c r="D7">
+        <v>1422.362594173718</v>
+      </c>
+      <c r="E7">
+        <v>-98.457512993213996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>69.73706783951603</v>
+      </c>
+      <c r="D8">
+        <v>1422.4374589364006</v>
+      </c>
+      <c r="E8">
+        <v>-98.454406059227281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17193DE-CB3F-4A1A-A76F-07CF188CD0FB}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>68.670531447005231</v>
+      </c>
+      <c r="D2">
+        <v>1421.6415342944949</v>
+      </c>
+      <c r="E2">
+        <v>-98.398742014732932</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>68.678513512608163</v>
+      </c>
+      <c r="D3">
+        <v>1421.6840747524468</v>
+      </c>
+      <c r="E3">
+        <v>-98.398555889097722</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>68.692489666294563</v>
+      </c>
+      <c r="D4">
+        <v>1421.7219858739461</v>
+      </c>
+      <c r="E4">
+        <v>-98.398229993444644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>68.719193694336852</v>
+      </c>
+      <c r="D5">
+        <v>1421.7759415482826</v>
+      </c>
+      <c r="E5">
+        <v>-98.397607309489217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>68.786270226123179</v>
+      </c>
+      <c r="D6">
+        <v>1421.8283415218609</v>
+      </c>
+      <c r="E6">
+        <v>-98.396043220354002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>68.858219842720899</v>
+      </c>
+      <c r="D7">
+        <v>1421.8872801971202</v>
+      </c>
+      <c r="E7">
+        <v>-98.394365500731226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>69.013407433657335</v>
+      </c>
+      <c r="D8">
+        <v>1421.9613704687488</v>
+      </c>
+      <c r="E8">
+        <v>-98.390746839801068</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C58E16-20AD-494D-A779-A5E7F93059D0}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>67.580728618945813</v>
+      </c>
+      <c r="D2">
+        <v>1421.6517792847246</v>
+      </c>
+      <c r="E2">
+        <v>-98.420032201881156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>67.59666937667086</v>
+      </c>
+      <c r="D3">
+        <v>1421.6922474778771</v>
+      </c>
+      <c r="E3">
+        <v>-98.419659523391331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>67.617321942754003</v>
+      </c>
+      <c r="D4">
+        <v>1421.73172625088</v>
+      </c>
+      <c r="E4">
+        <v>-98.419176687677265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>67.655022822300225</v>
+      </c>
+      <c r="D5">
+        <v>1421.7847877480224</v>
+      </c>
+      <c r="E5">
+        <v>-98.418295279961441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>67.740766456738228</v>
+      </c>
+      <c r="D6">
+        <v>1421.8370993662722</v>
+      </c>
+      <c r="E6">
+        <v>-98.416290682140826</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>67.832986039007054</v>
+      </c>
+      <c r="D7">
+        <v>1421.8967764317849</v>
+      </c>
+      <c r="E7">
+        <v>-98.414134683332918</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>68.023611875102489</v>
+      </c>
+      <c r="D8">
+        <v>1421.9688266100259</v>
+      </c>
+      <c r="E8">
+        <v>-98.409678047710969</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9859B5EF-276A-4045-9183-C942E6F3811F}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>68.403567729480429</v>
+      </c>
+      <c r="D2">
+        <v>1418.5415492308782</v>
+      </c>
+      <c r="E2">
+        <v>-98.338808369736995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>68.413539989812548</v>
+      </c>
+      <c r="D3">
+        <v>1418.5928946238873</v>
+      </c>
+      <c r="E3">
+        <v>-98.33856619179295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>68.432405768539965</v>
+      </c>
+      <c r="D4">
+        <v>1418.6242332114887</v>
+      </c>
+      <c r="E4">
+        <v>-98.338108033326066</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>68.464381732825089</v>
+      </c>
+      <c r="D5">
+        <v>1418.6730512822739</v>
+      </c>
+      <c r="E5">
+        <v>-98.337331491896975</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>68.528087909117872</v>
+      </c>
+      <c r="D6">
+        <v>1418.7351221153374</v>
+      </c>
+      <c r="E6">
+        <v>-98.335784377172303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>68.599923947505104</v>
+      </c>
+      <c r="D7">
+        <v>1418.7742006340179</v>
+      </c>
+      <c r="E7">
+        <v>-98.334039827440762</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>68.737647250464931</v>
+      </c>
+      <c r="D8">
+        <v>1418.8603499060537</v>
+      </c>
+      <c r="E8">
+        <v>-98.330695194905303</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23127461-8C50-4947-9028-D210EA79FEBE}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>66.93082089301025</v>
+      </c>
+      <c r="D2">
+        <v>1408.7624038292718</v>
+      </c>
+      <c r="E2">
+        <v>-98.292959226782671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>66.949188056740482</v>
+      </c>
+      <c r="D3">
+        <v>1408.795138335526</v>
+      </c>
+      <c r="E3">
+        <v>-98.292490780453193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>66.967225534469549</v>
+      </c>
+      <c r="D4">
+        <v>1408.8406467848602</v>
+      </c>
+      <c r="E4">
+        <v>-98.292030742618337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>67.008324781909707</v>
+      </c>
+      <c r="D5">
+        <v>1408.8850945548174</v>
+      </c>
+      <c r="E5">
+        <v>-98.290982524619608</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>67.094846367287772</v>
+      </c>
+      <c r="D6">
+        <v>1408.9529516141281</v>
+      </c>
+      <c r="E6">
+        <v>-98.28877583012472</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>67.193629676872462</v>
+      </c>
+      <c r="D7">
+        <v>1409.0095979632122</v>
+      </c>
+      <c r="E7">
+        <v>-98.286256405815763</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>67.394249599143933</v>
+      </c>
+      <c r="D8">
+        <v>1409.0849111742768</v>
+      </c>
+      <c r="E8">
+        <v>-98.281139684062367</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35EA58A-2F41-44D9-A649-49C68661F8C2}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>67.324730350935525</v>
+      </c>
+      <c r="D2">
+        <v>1408.1906593396966</v>
+      </c>
+      <c r="E2">
+        <v>-98.282648609963459</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>67.328727596905708</v>
+      </c>
+      <c r="D3">
+        <v>1408.2235496297531</v>
+      </c>
+      <c r="E3">
+        <v>-98.282546646303345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>67.330422134766337</v>
+      </c>
+      <c r="D4">
+        <v>1408.2710963645322</v>
+      </c>
+      <c r="E4">
+        <v>-98.282503421221946</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>67.346743432747374</v>
+      </c>
+      <c r="D5">
+        <v>1408.3182919149926</v>
+      </c>
+      <c r="E5">
+        <v>-98.282087089754611</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>67.390656657171988</v>
+      </c>
+      <c r="D6">
+        <v>1408.3846335128735</v>
+      </c>
+      <c r="E6">
+        <v>-98.280966930243935</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>67.451119868165563</v>
+      </c>
+      <c r="D7">
+        <v>1408.4422433788652</v>
+      </c>
+      <c r="E7">
+        <v>-98.279424605768142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>67.593658907367484</v>
+      </c>
+      <c r="D8">
+        <v>1408.515765906905</v>
+      </c>
+      <c r="E8">
+        <v>-98.275788651849979</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C132D2CE-3B24-45B6-9CA7-AB240779F56F}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>67.531945182174312</v>
+      </c>
+      <c r="D2">
+        <v>1407.290550697104</v>
+      </c>
+      <c r="E2">
+        <v>-98.229418983670627</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>67.526325277854085</v>
+      </c>
+      <c r="D3">
+        <v>1407.3334212333402</v>
+      </c>
+      <c r="E3">
+        <v>-98.229566328691931</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>67.524234059187904</v>
+      </c>
+      <c r="D4">
+        <v>1407.3699113118894</v>
+      </c>
+      <c r="E4">
+        <v>-98.229621157144777</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>67.533490591934381</v>
+      </c>
+      <c r="D5">
+        <v>1407.4031149039304</v>
+      </c>
+      <c r="E5">
+        <v>-98.229378465465842</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>67.557239525969493</v>
+      </c>
+      <c r="D6">
+        <v>1407.4816613860462</v>
+      </c>
+      <c r="E6">
+        <v>-98.228755805898629</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>67.6008007796909</v>
+      </c>
+      <c r="D7">
+        <v>1407.5288801658437</v>
+      </c>
+      <c r="E7">
+        <v>-98.227613698579219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>67.701248271899757</v>
+      </c>
+      <c r="D8">
+        <v>1407.6145830377698</v>
+      </c>
+      <c r="E8">
+        <v>-98.224980123870793</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B093FEE8-29BA-42C5-BEC2-96D1238B5950}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>67.450008313266736</v>
+      </c>
+      <c r="D2">
+        <v>1407.2123470081831</v>
+      </c>
+      <c r="E2">
+        <v>-98.225960041052986</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>67.446584600436452</v>
+      </c>
+      <c r="D3">
+        <v>1407.2674862729318</v>
+      </c>
+      <c r="E3">
+        <v>-98.226050090016969</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>67.452275705975481</v>
+      </c>
+      <c r="D4">
+        <v>1407.3017443573779</v>
+      </c>
+      <c r="E4">
+        <v>-98.225900405103815</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>67.467430210331003</v>
+      </c>
+      <c r="D5">
+        <v>1407.3493182560308</v>
+      </c>
+      <c r="E5">
+        <v>-98.225501818106466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>67.503997559345564</v>
+      </c>
+      <c r="D6">
+        <v>1407.4226541658791</v>
+      </c>
+      <c r="E6">
+        <v>-98.224540040043479</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>67.559013111154712</v>
+      </c>
+      <c r="D7">
+        <v>1407.4653811076428</v>
+      </c>
+      <c r="E7">
+        <v>-98.223093045599526</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>67.673691165923799</v>
+      </c>
+      <c r="D8">
+        <v>1407.5602299588179</v>
+      </c>
+      <c r="E8">
+        <v>-98.220076834680327</v>
       </c>
     </row>
   </sheetData>
@@ -8144,7 +11916,7 @@
         <v>1435.3531980861028</v>
       </c>
       <c r="E2">
-        <v>-0.78478755935791322</v>
+        <v>-99.378503510504586</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8161,7 +11933,7 @@
         <v>1435.3419998045761</v>
       </c>
       <c r="E3">
-        <v>-0.4892140330612989</v>
+        <v>-99.376652000998519</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -8178,7 +11950,7 @@
         <v>1435.3389662953643</v>
       </c>
       <c r="E4">
-        <v>-0.26435350165430566</v>
+        <v>-99.375243446529325</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -8195,7 +11967,7 @@
         <v>1435.3345339234734</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.373587503159129</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -8212,7 +11984,7 @@
         <v>1435.333728104599</v>
       </c>
       <c r="E6">
-        <v>0.32071542354669158</v>
+        <v>-99.371578501666747</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -8229,7 +12001,7 @@
         <v>1435.338707842282</v>
       </c>
       <c r="E7">
-        <v>0.57891920839009259</v>
+        <v>-99.369961080891159</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -8246,7 +12018,445 @@
         <v>1435.3575769095551</v>
       </c>
       <c r="E8">
-        <v>0.97907670648532408</v>
+        <v>-99.367454444316039</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DEF9F5C-FEF1-4817-80FD-FA7F59C5FDD8}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>67.212461882371983</v>
+      </c>
+      <c r="D2">
+        <v>1407.311857582567</v>
+      </c>
+      <c r="E2">
+        <v>-98.180508528785694</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>67.211501484061017</v>
+      </c>
+      <c r="D3">
+        <v>1407.3640189345917</v>
+      </c>
+      <c r="E3">
+        <v>-98.180534527484255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>67.221275476946417</v>
+      </c>
+      <c r="D4">
+        <v>1407.3948231280715</v>
+      </c>
+      <c r="E4">
+        <v>-98.18026993820726</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>67.240111386905113</v>
+      </c>
+      <c r="D5">
+        <v>1407.4432258930847</v>
+      </c>
+      <c r="E5">
+        <v>-98.179760036076573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>67.281601350039693</v>
+      </c>
+      <c r="D6">
+        <v>1407.5132961689046</v>
+      </c>
+      <c r="E6">
+        <v>-98.17863687183069</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>67.335089971874623</v>
+      </c>
+      <c r="D7">
+        <v>1407.5586115747672</v>
+      </c>
+      <c r="E7">
+        <v>-98.17718889494499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>67.445529123226677</v>
+      </c>
+      <c r="D8">
+        <v>1407.6601510136022</v>
+      </c>
+      <c r="E8">
+        <v>-98.174199224750723</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0548AC8-2CC2-4DE1-AA99-77333603E947}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>66.844928068224888</v>
+      </c>
+      <c r="D2">
+        <v>1402.1615956542348</v>
+      </c>
+      <c r="E2">
+        <v>-98.183328598098484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>66.839908709443876</v>
+      </c>
+      <c r="D3">
+        <v>1402.2068895724526</v>
+      </c>
+      <c r="E3">
+        <v>-98.183465011223859</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>66.844311702157484</v>
+      </c>
+      <c r="D4">
+        <v>1402.2308651060889</v>
+      </c>
+      <c r="E4">
+        <v>-98.183345349326132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>66.849698257224773</v>
+      </c>
+      <c r="D5">
+        <v>1402.2865213292293</v>
+      </c>
+      <c r="E5">
+        <v>-98.183198956760123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>66.878647945059242</v>
+      </c>
+      <c r="D6">
+        <v>1402.3482967563198</v>
+      </c>
+      <c r="E6">
+        <v>-98.182412179490655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>66.919924719462102</v>
+      </c>
+      <c r="D7">
+        <v>1402.4017894715892</v>
+      </c>
+      <c r="E7">
+        <v>-98.181290384048779</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>67.01761813129464</v>
+      </c>
+      <c r="D8">
+        <v>1402.4918446655352</v>
+      </c>
+      <c r="E8">
+        <v>-98.178635331039374</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7D1F6F-49AC-4B1A-BBA7-2D7E9001964B}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.3</v>
+      </c>
+      <c r="B2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C2">
+        <v>66.761797294606723</v>
+      </c>
+      <c r="D2">
+        <v>1399.1780243175647</v>
+      </c>
+      <c r="E2">
+        <v>-98.180645875232145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0.5</v>
+      </c>
+      <c r="B3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="C3">
+        <v>66.76115449854727</v>
+      </c>
+      <c r="D3">
+        <v>1399.2195098218647</v>
+      </c>
+      <c r="E3">
+        <v>-98.180663392340861</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.7</v>
+      </c>
+      <c r="B4">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="C4">
+        <v>66.767551011209875</v>
+      </c>
+      <c r="D4">
+        <v>1399.247749511002</v>
+      </c>
+      <c r="E4">
+        <v>-98.180489078254539</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1E-4</v>
+      </c>
+      <c r="C5">
+        <v>66.773550487637607</v>
+      </c>
+      <c r="D5">
+        <v>1399.3048562016888</v>
+      </c>
+      <c r="E5">
+        <v>-98.180325583971467</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5000000000000001E-4</v>
+      </c>
+      <c r="C6">
+        <v>66.803996229174032</v>
+      </c>
+      <c r="D6">
+        <v>1399.3631394686709</v>
+      </c>
+      <c r="E6">
+        <v>-98.179495894123519</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>66.843002740793963</v>
+      </c>
+      <c r="D7">
+        <v>1399.4234360919706</v>
+      </c>
+      <c r="E7">
+        <v>-98.178432911090042</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="C8">
+        <v>66.943389067873596</v>
+      </c>
+      <c r="D8">
+        <v>1399.5082179843439</v>
+      </c>
+      <c r="E8">
+        <v>-98.175697240607164</v>
       </c>
     </row>
   </sheetData>
@@ -8290,7 +12500,7 @@
         <v>1424.8703473793646</v>
       </c>
       <c r="E2">
-        <v>-0.62498215251035438</v>
+        <v>-99.373594312633315</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8307,7 +12517,7 @@
         <v>1424.8643051327858</v>
       </c>
       <c r="E3">
-        <v>-0.39023827142362083</v>
+        <v>-99.37211461577013</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -8324,7 +12534,7 @@
         <v>1424.85976966678</v>
       </c>
       <c r="E4">
-        <v>-0.20855536093741667</v>
+        <v>-99.370969386205488</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -8341,7 +12551,7 @@
         <v>1424.8550397411007</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.369654767430546</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -8358,7 +12568,7 @@
         <v>1424.8548773508758</v>
       </c>
       <c r="E6">
-        <v>0.28209764012072341</v>
+        <v>-99.367876578404847</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -8375,7 +12585,7 @@
         <v>1424.8645731026654</v>
       </c>
       <c r="E7">
-        <v>0.49836237747628254</v>
+        <v>-99.366513363943213</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -8392,7 +12602,7 @@
         <v>1424.8907170787722</v>
       </c>
       <c r="E8">
-        <v>0.84665073892073051</v>
+        <v>-99.364317944861241</v>
       </c>
     </row>
   </sheetData>
@@ -8436,7 +12646,7 @@
         <v>1418.3847067585809</v>
       </c>
       <c r="E2">
-        <v>-0.82688200516239607</v>
+        <v>-99.364839997246079</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8453,7 +12663,7 @@
         <v>1418.3816995527989</v>
       </c>
       <c r="E3">
-        <v>-0.52594330402686118</v>
+        <v>-99.362912617830077</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -8470,7 +12680,7 @@
         <v>1418.37711090575</v>
       </c>
       <c r="E4">
-        <v>-0.27949088915605891</v>
+        <v>-99.361334199003764</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -8487,7 +12697,7 @@
         <v>1418.3826365605742</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-99.359544183347168</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -8504,7 +12714,7 @@
         <v>1418.3971021868131</v>
       </c>
       <c r="E6">
-        <v>0.35257190329103166</v>
+        <v>-99.357286116084651</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -8521,7 +12731,7 @@
         <v>1418.413120673669</v>
       </c>
       <c r="E7">
-        <v>0.64716178467494834</v>
+        <v>-99.355399398054061</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -8538,7 +12748,7 @@
         <v>1418.4454655334232</v>
       </c>
       <c r="E8">
-        <v>1.1324402666591529</v>
+        <v>-99.352291403789209</v>
       </c>
     </row>
   </sheetData>
